--- a/HM.BST.xlsx
+++ b/HM.BST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4264B5A7-84D7-4711-939F-BC8808BC67E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BCD860-0583-47A2-93A6-19BBB0D55174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{A344954E-3009-47EB-94FE-5B6CEBCD1700}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
   <si>
     <t>H&amp;M</t>
   </si>
@@ -254,6 +254,21 @@
   <si>
     <t>Revenue Growth</t>
   </si>
+  <si>
+    <t>H&amp;M (Hennes &amp; Mauritz)</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -431,7 +446,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -459,6 +474,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -482,16 +498,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>33338</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>600076</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:rowOff>4763</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>42863</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>4763</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>90489</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -506,7 +522,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="9396413" y="119062"/>
+          <a:off x="12401551" y="4763"/>
           <a:ext cx="14287" cy="6562726"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -867,7 +883,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -878,7 +894,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="2">
-        <v>185.55</v>
+        <v>170.3</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -886,10 +902,10 @@
         <v>11</v>
       </c>
       <c r="I3" s="3">
-        <v>1604.0329999999999</v>
+        <v>1599.1559999999999</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -901,7 +917,7 @@
       </c>
       <c r="I4" s="6">
         <f>I3*I2</f>
-        <v>297628.32315000001</v>
+        <v>272336.26679999998</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -913,10 +929,10 @@
         <v>13</v>
       </c>
       <c r="I5" s="6">
-        <v>20908</v>
+        <v>18733</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -928,7 +944,7 @@
         <v>20675</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -940,7 +956,7 @@
       </c>
       <c r="I7" s="6">
         <f>I4+I6-I5</f>
-        <v>297395.32315000001</v>
+        <v>274278.26679999998</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -996,22 +1012,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156BA011-9419-4A0D-9DFA-1101D03AF4DD}">
-  <dimension ref="A1:CO281"/>
+  <dimension ref="A1:CS281"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="2" customWidth="1"/>
-    <col min="3" max="16" width="9.140625" style="2"/>
-    <col min="17" max="18" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="20" width="9.140625" style="2"/>
+    <col min="21" max="22" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:97" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:97" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
@@ -1048,23 +1064,35 @@
       <c r="N2" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="P2" s="2">
+      <c r="O2" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="T2" s="2">
         <v>2021</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="U2" s="2">
         <v>2022</v>
       </c>
-      <c r="R2" s="2">
+      <c r="V2" s="2">
         <v>2023</v>
       </c>
-      <c r="S2" s="2">
+      <c r="W2" s="2">
         <v>2024</v>
       </c>
-      <c r="T2" s="2">
+      <c r="X2" s="2">
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B3" s="16" t="s">
         <v>55</v>
       </c>
@@ -1104,26 +1132,28 @@
       <c r="N3" s="16">
         <v>3660</v>
       </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16">
+      <c r="O3" s="16">
+        <v>3616</v>
+      </c>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16">
         <v>4242</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="U3" s="16">
         <v>3947</v>
       </c>
-      <c r="R3" s="16">
+      <c r="V3" s="16">
         <v>3872</v>
       </c>
-      <c r="S3" s="16">
+      <c r="W3" s="16">
         <v>3777</v>
       </c>
-      <c r="T3" s="16">
+      <c r="X3" s="16">
         <v>3660</v>
       </c>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
       <c r="Y3" s="16"/>
       <c r="Z3" s="16"/>
       <c r="AA3" s="16"/>
@@ -1134,10 +1164,10 @@
       <c r="AF3" s="16"/>
       <c r="AG3" s="16"/>
       <c r="AH3" s="16"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
+      <c r="AI3" s="16"/>
+      <c r="AJ3" s="16"/>
+      <c r="AK3" s="16"/>
+      <c r="AL3" s="16"/>
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
@@ -1193,8 +1223,12 @@
       <c r="CM3" s="3"/>
       <c r="CN3" s="3"/>
       <c r="CO3" s="3"/>
+      <c r="CP3" s="3"/>
+      <c r="CQ3" s="3"/>
+      <c r="CR3" s="3"/>
+      <c r="CS3" s="3"/>
     </row>
-    <row r="4" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B4" s="16" t="s">
         <v>57</v>
       </c>
@@ -1234,26 +1268,28 @@
       <c r="N4" s="16">
         <v>246</v>
       </c>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16">
+      <c r="O4" s="16">
+        <v>247</v>
+      </c>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16">
         <v>275</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="U4" s="16">
         <v>259</v>
       </c>
-      <c r="R4" s="16">
+      <c r="V4" s="16">
         <v>245</v>
       </c>
-      <c r="S4" s="16">
+      <c r="W4" s="16">
         <v>238</v>
       </c>
-      <c r="T4" s="16">
+      <c r="X4" s="16">
         <v>246</v>
       </c>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
       <c r="Y4" s="16"/>
       <c r="Z4" s="16"/>
       <c r="AA4" s="16"/>
@@ -1264,10 +1300,10 @@
       <c r="AF4" s="16"/>
       <c r="AG4" s="16"/>
       <c r="AH4" s="16"/>
-      <c r="AI4" s="3"/>
-      <c r="AJ4" s="3"/>
-      <c r="AK4" s="3"/>
-      <c r="AL4" s="3"/>
+      <c r="AI4" s="16"/>
+      <c r="AJ4" s="16"/>
+      <c r="AK4" s="16"/>
+      <c r="AL4" s="16"/>
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
@@ -1323,8 +1359,12 @@
       <c r="CM4" s="3"/>
       <c r="CN4" s="3"/>
       <c r="CO4" s="3"/>
+      <c r="CP4" s="3"/>
+      <c r="CQ4" s="3"/>
+      <c r="CR4" s="3"/>
+      <c r="CS4" s="3"/>
     </row>
-    <row r="5" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
         <v>58</v>
       </c>
@@ -1364,26 +1404,28 @@
       <c r="N5" s="16">
         <v>0</v>
       </c>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16">
+      <c r="O5" s="16">
+        <v>0</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16">
         <v>98</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="U5" s="16">
         <v>78</v>
       </c>
-      <c r="R5" s="16">
+      <c r="V5" s="16">
         <v>64</v>
       </c>
-      <c r="S5" s="16">
+      <c r="W5" s="16">
         <v>48</v>
       </c>
-      <c r="T5" s="16">
+      <c r="X5" s="16">
         <v>0</v>
       </c>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
       <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
       <c r="AA5" s="16"/>
@@ -1394,10 +1436,10 @@
       <c r="AF5" s="16"/>
       <c r="AG5" s="16"/>
       <c r="AH5" s="16"/>
-      <c r="AI5" s="3"/>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
+      <c r="AI5" s="16"/>
+      <c r="AJ5" s="16"/>
+      <c r="AK5" s="16"/>
+      <c r="AL5" s="16"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
@@ -1453,8 +1495,12 @@
       <c r="CM5" s="3"/>
       <c r="CN5" s="3"/>
       <c r="CO5" s="3"/>
+      <c r="CP5" s="3"/>
+      <c r="CQ5" s="3"/>
+      <c r="CR5" s="3"/>
+      <c r="CS5" s="3"/>
     </row>
-    <row r="6" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B6" s="16" t="s">
         <v>59</v>
       </c>
@@ -1494,26 +1540,28 @@
       <c r="N6" s="16">
         <v>44</v>
       </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16">
+      <c r="O6" s="16">
+        <v>43</v>
+      </c>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="16">
         <v>57</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="U6" s="16">
         <v>54</v>
       </c>
-      <c r="R6" s="16">
+      <c r="V6" s="16">
         <v>53</v>
       </c>
-      <c r="S6" s="16">
+      <c r="W6" s="16">
         <v>46</v>
       </c>
-      <c r="T6" s="16">
+      <c r="X6" s="16">
         <v>44</v>
       </c>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
       <c r="Y6" s="16"/>
       <c r="Z6" s="16"/>
       <c r="AA6" s="16"/>
@@ -1524,10 +1572,10 @@
       <c r="AF6" s="16"/>
       <c r="AG6" s="16"/>
       <c r="AH6" s="16"/>
-      <c r="AI6" s="3"/>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
+      <c r="AI6" s="16"/>
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="16"/>
+      <c r="AL6" s="16"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
@@ -1583,8 +1631,12 @@
       <c r="CM6" s="3"/>
       <c r="CN6" s="3"/>
       <c r="CO6" s="3"/>
+      <c r="CP6" s="3"/>
+      <c r="CQ6" s="3"/>
+      <c r="CR6" s="3"/>
+      <c r="CS6" s="3"/>
     </row>
-    <row r="7" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B7" s="16" t="s">
         <v>60</v>
       </c>
@@ -1624,26 +1676,28 @@
       <c r="N7" s="16">
         <v>66</v>
       </c>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16">
+      <c r="O7" s="16">
+        <v>66</v>
+      </c>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16">
         <v>78</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="U7" s="16">
         <v>71</v>
       </c>
-      <c r="R7" s="16">
+      <c r="V7" s="16">
         <v>72</v>
       </c>
-      <c r="S7" s="16">
+      <c r="W7" s="16">
         <v>70</v>
       </c>
-      <c r="T7" s="16">
+      <c r="X7" s="16">
         <v>66</v>
       </c>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
       <c r="Y7" s="16"/>
       <c r="Z7" s="16"/>
       <c r="AA7" s="16"/>
@@ -1654,10 +1708,10 @@
       <c r="AF7" s="16"/>
       <c r="AG7" s="16"/>
       <c r="AH7" s="16"/>
-      <c r="AI7" s="3"/>
-      <c r="AJ7" s="3"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="3"/>
+      <c r="AI7" s="16"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
+      <c r="AL7" s="16"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
@@ -1713,8 +1767,12 @@
       <c r="CM7" s="3"/>
       <c r="CN7" s="3"/>
       <c r="CO7" s="3"/>
+      <c r="CP7" s="3"/>
+      <c r="CQ7" s="3"/>
+      <c r="CR7" s="3"/>
+      <c r="CS7" s="3"/>
     </row>
-    <row r="8" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B8" s="16" t="s">
         <v>61</v>
       </c>
@@ -1754,26 +1812,28 @@
       <c r="N8" s="16">
         <v>53</v>
       </c>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16">
+      <c r="O8" s="16">
+        <v>54</v>
+      </c>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16">
         <v>24</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="U8" s="16">
         <v>25</v>
       </c>
-      <c r="R8" s="16">
+      <c r="V8" s="16">
         <v>30</v>
       </c>
-      <c r="S8" s="16">
+      <c r="W8" s="16">
         <v>40</v>
       </c>
-      <c r="T8" s="16">
+      <c r="X8" s="16">
         <v>53</v>
       </c>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
       <c r="Y8" s="16"/>
       <c r="Z8" s="16"/>
       <c r="AA8" s="16"/>
@@ -1784,10 +1844,10 @@
       <c r="AF8" s="16"/>
       <c r="AG8" s="16"/>
       <c r="AH8" s="16"/>
-      <c r="AI8" s="3"/>
-      <c r="AJ8" s="3"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="16"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
       <c r="AO8" s="3"/>
@@ -1843,8 +1903,12 @@
       <c r="CM8" s="3"/>
       <c r="CN8" s="3"/>
       <c r="CO8" s="3"/>
+      <c r="CP8" s="3"/>
+      <c r="CQ8" s="3"/>
+      <c r="CR8" s="3"/>
+      <c r="CS8" s="3"/>
     </row>
-    <row r="9" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B9" s="16" t="s">
         <v>62</v>
       </c>
@@ -1884,26 +1948,28 @@
       <c r="N9" s="16">
         <v>0</v>
       </c>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16">
+      <c r="O9" s="16">
         <v>0</v>
       </c>
-      <c r="Q9" s="16">
-        <v>0</v>
-      </c>
-      <c r="R9" s="16">
-        <v>0</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0</v>
-      </c>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
       <c r="T9" s="16">
         <v>0</v>
       </c>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
+      <c r="U9" s="16">
+        <v>0</v>
+      </c>
+      <c r="V9" s="16">
+        <v>0</v>
+      </c>
+      <c r="W9" s="16">
+        <v>0</v>
+      </c>
+      <c r="X9" s="16">
+        <v>0</v>
+      </c>
       <c r="Y9" s="16"/>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
@@ -1914,10 +1980,10 @@
       <c r="AF9" s="16"/>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="16"/>
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
@@ -1973,8 +2039,12 @@
       <c r="CM9" s="3"/>
       <c r="CN9" s="3"/>
       <c r="CO9" s="3"/>
+      <c r="CP9" s="3"/>
+      <c r="CQ9" s="3"/>
+      <c r="CR9" s="3"/>
+      <c r="CS9" s="3"/>
     </row>
-    <row r="10" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B10" s="16" t="s">
         <v>63</v>
       </c>
@@ -2014,26 +2084,28 @@
       <c r="N10" s="16">
         <v>32</v>
       </c>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16">
+      <c r="O10" s="16">
+        <v>24</v>
+      </c>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16">
         <v>27</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="U10" s="16">
         <v>31</v>
       </c>
-      <c r="R10" s="16">
+      <c r="V10" s="16">
         <v>33</v>
       </c>
-      <c r="S10" s="16">
+      <c r="W10" s="16">
         <v>34</v>
       </c>
-      <c r="T10" s="16">
+      <c r="X10" s="16">
         <v>32</v>
       </c>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
       <c r="Y10" s="16"/>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
@@ -2044,10 +2116,10 @@
       <c r="AF10" s="16"/>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
-      <c r="AI10" s="3"/>
-      <c r="AJ10" s="3"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="3"/>
+      <c r="AI10" s="16"/>
+      <c r="AJ10" s="16"/>
+      <c r="AK10" s="16"/>
+      <c r="AL10" s="16"/>
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
@@ -2103,8 +2175,12 @@
       <c r="CM10" s="3"/>
       <c r="CN10" s="3"/>
       <c r="CO10" s="3"/>
+      <c r="CP10" s="3"/>
+      <c r="CQ10" s="3"/>
+      <c r="CR10" s="3"/>
+      <c r="CS10" s="3"/>
     </row>
-    <row r="11" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
         <v>64</v>
       </c>
@@ -2144,26 +2220,28 @@
       <c r="N11" s="16">
         <v>0</v>
       </c>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16">
+      <c r="O11" s="16">
         <v>0</v>
       </c>
-      <c r="Q11" s="16">
-        <v>0</v>
-      </c>
-      <c r="R11" s="16">
-        <v>0</v>
-      </c>
-      <c r="S11" s="16">
-        <v>0</v>
-      </c>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
       <c r="T11" s="16">
         <v>0</v>
       </c>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
+      <c r="U11" s="16">
+        <v>0</v>
+      </c>
+      <c r="V11" s="16">
+        <v>0</v>
+      </c>
+      <c r="W11" s="16">
+        <v>0</v>
+      </c>
+      <c r="X11" s="16">
+        <v>0</v>
+      </c>
       <c r="Y11" s="16"/>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
@@ -2174,10 +2252,10 @@
       <c r="AF11" s="16"/>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="16"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
@@ -2233,8 +2311,12 @@
       <c r="CM11" s="3"/>
       <c r="CN11" s="3"/>
       <c r="CO11" s="3"/>
+      <c r="CP11" s="3"/>
+      <c r="CQ11" s="3"/>
+      <c r="CR11" s="3"/>
+      <c r="CS11" s="3"/>
     </row>
-    <row r="12" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
         <v>42</v>
       </c>
@@ -2274,26 +2356,28 @@
       <c r="N12" s="16">
         <v>357</v>
       </c>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16">
+      <c r="O12" s="16">
+        <v>356</v>
+      </c>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16">
         <v>427</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="U12" s="16">
         <v>399</v>
       </c>
-      <c r="R12" s="16">
+      <c r="V12" s="16">
         <v>389</v>
       </c>
-      <c r="S12" s="16">
+      <c r="W12" s="16">
         <v>380</v>
       </c>
-      <c r="T12" s="16">
+      <c r="X12" s="16">
         <v>357</v>
       </c>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
       <c r="Z12" s="16"/>
       <c r="AA12" s="16"/>
@@ -2304,10 +2388,10 @@
       <c r="AF12" s="16"/>
       <c r="AG12" s="16"/>
       <c r="AH12" s="16"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
@@ -2363,8 +2447,12 @@
       <c r="CM12" s="3"/>
       <c r="CN12" s="3"/>
       <c r="CO12" s="3"/>
+      <c r="CP12" s="3"/>
+      <c r="CQ12" s="3"/>
+      <c r="CR12" s="3"/>
+      <c r="CS12" s="3"/>
     </row>
-    <row r="13" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
         <v>43</v>
       </c>
@@ -2404,26 +2492,28 @@
       <c r="N13" s="16">
         <v>994</v>
       </c>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16">
+      <c r="O13" s="16">
+        <v>986</v>
+      </c>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16">
         <v>1127</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="U13" s="16">
         <v>1079</v>
       </c>
-      <c r="R13" s="16">
+      <c r="V13" s="16">
         <v>1051</v>
       </c>
-      <c r="S13" s="16">
+      <c r="W13" s="16">
         <v>1016</v>
       </c>
-      <c r="T13" s="16">
+      <c r="X13" s="16">
         <v>994</v>
       </c>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
       <c r="AA13" s="16"/>
@@ -2434,10 +2524,10 @@
       <c r="AF13" s="16"/>
       <c r="AG13" s="16"/>
       <c r="AH13" s="16"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="16"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
@@ -2493,8 +2583,12 @@
       <c r="CM13" s="3"/>
       <c r="CN13" s="3"/>
       <c r="CO13" s="3"/>
+      <c r="CP13" s="3"/>
+      <c r="CQ13" s="3"/>
+      <c r="CR13" s="3"/>
+      <c r="CS13" s="3"/>
     </row>
-    <row r="14" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
         <v>44</v>
       </c>
@@ -2534,26 +2628,28 @@
       <c r="N14" s="16">
         <v>478</v>
       </c>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16">
+      <c r="O14" s="16">
+        <v>474</v>
+      </c>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16">
         <v>653</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="U14" s="16">
         <v>481</v>
       </c>
-      <c r="R14" s="16">
+      <c r="V14" s="16">
         <v>475</v>
       </c>
-      <c r="S14" s="16">
+      <c r="W14" s="16">
         <v>479</v>
       </c>
-      <c r="T14" s="16">
+      <c r="X14" s="16">
         <v>478</v>
       </c>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
       <c r="AA14" s="16"/>
@@ -2564,10 +2660,10 @@
       <c r="AF14" s="16"/>
       <c r="AG14" s="16"/>
       <c r="AH14" s="16"/>
-      <c r="AI14" s="3"/>
-      <c r="AJ14" s="3"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="3"/>
+      <c r="AI14" s="16"/>
+      <c r="AJ14" s="16"/>
+      <c r="AK14" s="16"/>
+      <c r="AL14" s="16"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
@@ -2623,8 +2719,12 @@
       <c r="CM14" s="3"/>
       <c r="CN14" s="3"/>
       <c r="CO14" s="3"/>
+      <c r="CP14" s="3"/>
+      <c r="CQ14" s="3"/>
+      <c r="CR14" s="3"/>
+      <c r="CS14" s="3"/>
     </row>
-    <row r="15" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
         <v>53</v>
       </c>
@@ -2664,26 +2764,28 @@
       <c r="N15" s="16">
         <v>563</v>
       </c>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16">
+      <c r="O15" s="16">
+        <v>562</v>
+      </c>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16">
         <v>650</v>
       </c>
-      <c r="Q15" s="16">
+      <c r="U15" s="16">
         <v>623</v>
       </c>
-      <c r="R15" s="16">
+      <c r="V15" s="16">
         <v>608</v>
       </c>
-      <c r="S15" s="16">
+      <c r="W15" s="16">
         <v>574</v>
       </c>
-      <c r="T15" s="16">
+      <c r="X15" s="16">
         <v>563</v>
       </c>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
       <c r="AA15" s="16"/>
@@ -2694,10 +2796,10 @@
       <c r="AF15" s="16"/>
       <c r="AG15" s="16"/>
       <c r="AH15" s="16"/>
-      <c r="AI15" s="3"/>
-      <c r="AJ15" s="3"/>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="3"/>
+      <c r="AI15" s="16"/>
+      <c r="AJ15" s="16"/>
+      <c r="AK15" s="16"/>
+      <c r="AL15" s="16"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
@@ -2753,8 +2855,12 @@
       <c r="CM15" s="3"/>
       <c r="CN15" s="3"/>
       <c r="CO15" s="3"/>
+      <c r="CP15" s="3"/>
+      <c r="CQ15" s="3"/>
+      <c r="CR15" s="3"/>
+      <c r="CS15" s="3"/>
     </row>
-    <row r="16" spans="1:93" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:97" x14ac:dyDescent="0.2">
       <c r="B16" s="16" t="s">
         <v>45</v>
       </c>
@@ -2794,26 +2900,28 @@
       <c r="N16" s="16">
         <v>769</v>
       </c>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16">
+      <c r="O16" s="16">
         <v>757</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16">
+        <v>757</v>
+      </c>
+      <c r="U16" s="16">
         <v>740</v>
       </c>
-      <c r="R16" s="16">
+      <c r="V16" s="16">
         <v>745</v>
       </c>
-      <c r="S16" s="16">
+      <c r="W16" s="16">
         <v>759</v>
       </c>
-      <c r="T16" s="16">
+      <c r="X16" s="16">
         <v>769</v>
       </c>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
       <c r="Y16" s="16"/>
       <c r="Z16" s="16"/>
       <c r="AA16" s="16"/>
@@ -2824,10 +2932,10 @@
       <c r="AF16" s="16"/>
       <c r="AG16" s="16"/>
       <c r="AH16" s="16"/>
-      <c r="AI16" s="3"/>
-      <c r="AJ16" s="3"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="3"/>
+      <c r="AI16" s="16"/>
+      <c r="AJ16" s="16"/>
+      <c r="AK16" s="16"/>
+      <c r="AL16" s="16"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
@@ -2883,8 +2991,12 @@
       <c r="CM16" s="3"/>
       <c r="CN16" s="3"/>
       <c r="CO16" s="3"/>
+      <c r="CP16" s="3"/>
+      <c r="CQ16" s="3"/>
+      <c r="CR16" s="3"/>
+      <c r="CS16" s="3"/>
     </row>
-    <row r="17" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B17" s="16" t="s">
         <v>46</v>
       </c>
@@ -2924,26 +3036,28 @@
       <c r="N17" s="16">
         <v>940</v>
       </c>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16">
+      <c r="O17" s="16">
+        <v>915</v>
+      </c>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16">
         <v>1187</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="U17" s="16">
         <v>1143</v>
       </c>
-      <c r="R17" s="16">
+      <c r="V17" s="16">
         <v>1101</v>
       </c>
-      <c r="S17" s="16">
+      <c r="W17" s="16">
         <v>1045</v>
       </c>
-      <c r="T17" s="16">
+      <c r="X17" s="16">
         <v>940</v>
       </c>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
       <c r="Y17" s="16"/>
       <c r="Z17" s="16"/>
       <c r="AA17" s="16"/>
@@ -2954,10 +3068,10 @@
       <c r="AF17" s="16"/>
       <c r="AG17" s="16"/>
       <c r="AH17" s="16"/>
-      <c r="AI17" s="3"/>
-      <c r="AJ17" s="3"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="3"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="16"/>
       <c r="AM17" s="3"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
@@ -3013,8 +3127,12 @@
       <c r="CM17" s="3"/>
       <c r="CN17" s="3"/>
       <c r="CO17" s="3"/>
+      <c r="CP17" s="3"/>
+      <c r="CQ17" s="3"/>
+      <c r="CR17" s="3"/>
+      <c r="CS17" s="3"/>
     </row>
-    <row r="18" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B18" s="17" t="s">
         <v>54</v>
       </c>
@@ -3054,31 +3172,33 @@
       <c r="N18" s="17">
         <v>4101</v>
       </c>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17">
-        <f t="shared" ref="P18:R18" si="0">+SUM(P12:P17)</f>
+      <c r="O18" s="17">
+        <v>4050</v>
+      </c>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17">
+        <f t="shared" ref="T18:V18" si="0">+SUM(T12:T17)</f>
         <v>4801</v>
       </c>
-      <c r="Q18" s="17">
+      <c r="U18" s="17">
         <f t="shared" si="0"/>
         <v>4465</v>
       </c>
-      <c r="R18" s="17">
+      <c r="V18" s="17">
         <f t="shared" si="0"/>
         <v>4369</v>
       </c>
-      <c r="S18" s="17">
-        <f>+SUM(S12:S17)</f>
+      <c r="W18" s="17">
+        <f>+SUM(W12:W17)</f>
         <v>4253</v>
       </c>
-      <c r="T18" s="17">
-        <f>+SUM(T12:T17)</f>
+      <c r="X18" s="17">
+        <f>+SUM(X12:X17)</f>
         <v>4101</v>
       </c>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
       <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
       <c r="AA18" s="16"/>
@@ -3089,10 +3209,10 @@
       <c r="AF18" s="16"/>
       <c r="AG18" s="16"/>
       <c r="AH18" s="16"/>
-      <c r="AI18" s="3"/>
-      <c r="AJ18" s="3"/>
-      <c r="AK18" s="3"/>
-      <c r="AL18" s="3"/>
+      <c r="AI18" s="16"/>
+      <c r="AJ18" s="16"/>
+      <c r="AK18" s="16"/>
+      <c r="AL18" s="16"/>
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
@@ -3148,8 +3268,12 @@
       <c r="CM18" s="3"/>
       <c r="CN18" s="3"/>
       <c r="CO18" s="3"/>
+      <c r="CP18" s="3"/>
+      <c r="CQ18" s="3"/>
+      <c r="CR18" s="3"/>
+      <c r="CS18" s="3"/>
     </row>
-    <row r="19" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -3183,10 +3307,10 @@
       <c r="AF19" s="16"/>
       <c r="AG19" s="16"/>
       <c r="AH19" s="16"/>
-      <c r="AI19" s="3"/>
-      <c r="AJ19" s="3"/>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="3"/>
+      <c r="AI19" s="16"/>
+      <c r="AJ19" s="16"/>
+      <c r="AK19" s="16"/>
+      <c r="AL19" s="16"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
@@ -3242,8 +3366,12 @@
       <c r="CM19" s="3"/>
       <c r="CN19" s="3"/>
       <c r="CO19" s="3"/>
+      <c r="CP19" s="3"/>
+      <c r="CQ19" s="3"/>
+      <c r="CR19" s="3"/>
+      <c r="CS19" s="3"/>
     </row>
-    <row r="20" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B20" s="16" t="s">
         <v>47</v>
       </c>
@@ -3257,7 +3385,7 @@
         <v>5809</v>
       </c>
       <c r="F20" s="16">
-        <f>+R20-SUM(C20:E20)</f>
+        <f>+V20-SUM(C20:E20)</f>
         <v>5353</v>
       </c>
       <c r="G20" s="16">
@@ -3270,7 +3398,7 @@
         <v>5313</v>
       </c>
       <c r="J20" s="16">
-        <f>+S20-SUM(G20:I20)</f>
+        <f>+W20-SUM(G20:I20)</f>
         <v>5127</v>
       </c>
       <c r="K20" s="16">
@@ -3285,22 +3413,24 @@
       <c r="N20" s="16">
         <v>5133</v>
       </c>
-      <c r="O20" s="16"/>
+      <c r="O20" s="16">
+        <v>4473</v>
+      </c>
       <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
-      <c r="R20" s="16">
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16">
         <v>21307</v>
       </c>
-      <c r="S20" s="16">
+      <c r="W20" s="16">
         <v>20627</v>
       </c>
-      <c r="T20" s="16">
+      <c r="X20" s="16">
         <v>20147</v>
       </c>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
       <c r="Y20" s="16"/>
       <c r="Z20" s="16"/>
       <c r="AA20" s="16"/>
@@ -3311,10 +3441,10 @@
       <c r="AF20" s="16"/>
       <c r="AG20" s="16"/>
       <c r="AH20" s="16"/>
-      <c r="AI20" s="3"/>
-      <c r="AJ20" s="3"/>
-      <c r="AK20" s="3"/>
-      <c r="AL20" s="3"/>
+      <c r="AI20" s="16"/>
+      <c r="AJ20" s="16"/>
+      <c r="AK20" s="16"/>
+      <c r="AL20" s="16"/>
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
@@ -3370,8 +3500,12 @@
       <c r="CM20" s="3"/>
       <c r="CN20" s="3"/>
       <c r="CO20" s="3"/>
+      <c r="CP20" s="3"/>
+      <c r="CQ20" s="3"/>
+      <c r="CR20" s="3"/>
+      <c r="CS20" s="3"/>
     </row>
-    <row r="21" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B21" s="16" t="s">
         <v>48</v>
       </c>
@@ -3385,7 +3519,7 @@
         <v>20581</v>
       </c>
       <c r="F21" s="16">
-        <f t="shared" ref="F21:F37" si="1">+R21-SUM(C21:E21)</f>
+        <f t="shared" ref="F21:F37" si="1">+V21-SUM(C21:E21)</f>
         <v>21326</v>
       </c>
       <c r="G21" s="16">
@@ -3398,7 +3532,7 @@
         <v>19731</v>
       </c>
       <c r="J21" s="16">
-        <f t="shared" ref="J21:J37" si="2">+S21-SUM(G21:I21)</f>
+        <f t="shared" ref="J21:J37" si="2">+W21-SUM(G21:I21)</f>
         <v>22054</v>
       </c>
       <c r="K21" s="16">
@@ -3413,22 +3547,24 @@
       <c r="N21" s="16">
         <v>21433</v>
       </c>
-      <c r="O21" s="16"/>
+      <c r="O21" s="16">
+        <v>16557</v>
+      </c>
       <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
-      <c r="R21" s="16">
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16">
         <v>79049</v>
       </c>
-      <c r="S21" s="16">
+      <c r="W21" s="16">
         <v>79550</v>
       </c>
-      <c r="T21" s="16">
+      <c r="X21" s="16">
         <v>79195</v>
       </c>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
       <c r="Y21" s="16"/>
       <c r="Z21" s="16"/>
       <c r="AA21" s="16"/>
@@ -3439,10 +3575,10 @@
       <c r="AF21" s="16"/>
       <c r="AG21" s="16"/>
       <c r="AH21" s="16"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="3"/>
-      <c r="AK21" s="3"/>
-      <c r="AL21" s="3"/>
+      <c r="AI21" s="16"/>
+      <c r="AJ21" s="16"/>
+      <c r="AK21" s="16"/>
+      <c r="AL21" s="16"/>
       <c r="AM21" s="3"/>
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
@@ -3498,8 +3634,12 @@
       <c r="CM21" s="3"/>
       <c r="CN21" s="3"/>
       <c r="CO21" s="3"/>
+      <c r="CP21" s="3"/>
+      <c r="CQ21" s="3"/>
+      <c r="CR21" s="3"/>
+      <c r="CS21" s="3"/>
     </row>
-    <row r="22" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
         <v>49</v>
       </c>
@@ -3541,22 +3681,24 @@
       <c r="N22" s="16">
         <v>5683</v>
       </c>
-      <c r="O22" s="16"/>
+      <c r="O22" s="16">
+        <v>4419</v>
+      </c>
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
-      <c r="R22" s="16">
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16">
         <v>19633</v>
       </c>
-      <c r="S22" s="16">
+      <c r="W22" s="16">
         <v>21181</v>
       </c>
-      <c r="T22" s="16">
+      <c r="X22" s="16">
         <v>20934</v>
       </c>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
       <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
       <c r="AA22" s="16"/>
@@ -3567,10 +3709,10 @@
       <c r="AF22" s="16"/>
       <c r="AG22" s="16"/>
       <c r="AH22" s="16"/>
-      <c r="AI22" s="3"/>
-      <c r="AJ22" s="3"/>
-      <c r="AK22" s="3"/>
-      <c r="AL22" s="3"/>
+      <c r="AI22" s="16"/>
+      <c r="AJ22" s="16"/>
+      <c r="AK22" s="16"/>
+      <c r="AL22" s="16"/>
       <c r="AM22" s="3"/>
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
@@ -3626,8 +3768,12 @@
       <c r="CM22" s="3"/>
       <c r="CN22" s="3"/>
       <c r="CO22" s="3"/>
+      <c r="CP22" s="3"/>
+      <c r="CQ22" s="3"/>
+      <c r="CR22" s="3"/>
+      <c r="CS22" s="3"/>
     </row>
-    <row r="23" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B23" s="16" t="s">
         <v>50</v>
       </c>
@@ -3669,22 +3815,24 @@
       <c r="N23" s="16">
         <v>8520</v>
       </c>
-      <c r="O23" s="16"/>
+      <c r="O23" s="16">
+        <v>6837</v>
+      </c>
       <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
-      <c r="R23" s="16">
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16">
         <v>31186</v>
       </c>
-      <c r="S23" s="16">
+      <c r="W23" s="16">
         <v>31507</v>
       </c>
-      <c r="T23" s="16">
+      <c r="X23" s="16">
         <v>31271</v>
       </c>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
       <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
       <c r="AA23" s="16"/>
@@ -3695,10 +3843,10 @@
       <c r="AF23" s="16"/>
       <c r="AG23" s="16"/>
       <c r="AH23" s="16"/>
-      <c r="AI23" s="3"/>
-      <c r="AJ23" s="3"/>
-      <c r="AK23" s="3"/>
-      <c r="AL23" s="3"/>
+      <c r="AI23" s="16"/>
+      <c r="AJ23" s="16"/>
+      <c r="AK23" s="16"/>
+      <c r="AL23" s="16"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
@@ -3754,8 +3902,12 @@
       <c r="CM23" s="3"/>
       <c r="CN23" s="3"/>
       <c r="CO23" s="3"/>
+      <c r="CP23" s="3"/>
+      <c r="CQ23" s="3"/>
+      <c r="CR23" s="3"/>
+      <c r="CS23" s="3"/>
     </row>
-    <row r="24" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B24" s="16" t="s">
         <v>51</v>
       </c>
@@ -3797,22 +3949,24 @@
       <c r="N24" s="16">
         <v>11692</v>
       </c>
-      <c r="O24" s="16"/>
+      <c r="O24" s="16">
+        <v>11172</v>
+      </c>
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
-      <c r="R24" s="16">
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16">
         <v>53785</v>
       </c>
-      <c r="S24" s="16">
+      <c r="W24" s="16">
         <v>51798</v>
       </c>
-      <c r="T24" s="16">
+      <c r="X24" s="16">
         <v>48999</v>
       </c>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
       <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
       <c r="AA24" s="16"/>
@@ -3823,10 +3977,10 @@
       <c r="AF24" s="16"/>
       <c r="AG24" s="16"/>
       <c r="AH24" s="16"/>
-      <c r="AI24" s="3"/>
-      <c r="AJ24" s="3"/>
-      <c r="AK24" s="3"/>
-      <c r="AL24" s="3"/>
+      <c r="AI24" s="16"/>
+      <c r="AJ24" s="16"/>
+      <c r="AK24" s="16"/>
+      <c r="AL24" s="16"/>
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
@@ -3882,8 +4036,12 @@
       <c r="CM24" s="3"/>
       <c r="CN24" s="3"/>
       <c r="CO24" s="3"/>
+      <c r="CP24" s="3"/>
+      <c r="CQ24" s="3"/>
+      <c r="CR24" s="3"/>
+      <c r="CS24" s="3"/>
     </row>
-    <row r="25" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B25" s="16" t="s">
         <v>52</v>
       </c>
@@ -3925,22 +4083,24 @@
       <c r="N25" s="16">
         <v>6760</v>
       </c>
-      <c r="O25" s="16"/>
+      <c r="O25" s="16">
+        <v>6149</v>
+      </c>
       <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
-      <c r="R25" s="16">
+      <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
+      <c r="T25" s="16"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="16">
         <v>31075</v>
       </c>
-      <c r="S25" s="16">
+      <c r="W25" s="16">
         <v>29815</v>
       </c>
-      <c r="T25" s="16">
+      <c r="X25" s="16">
         <v>27729</v>
       </c>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
       <c r="Y25" s="16"/>
       <c r="Z25" s="16"/>
       <c r="AA25" s="16"/>
@@ -3951,10 +4111,10 @@
       <c r="AF25" s="16"/>
       <c r="AG25" s="16"/>
       <c r="AH25" s="16"/>
-      <c r="AI25" s="3"/>
-      <c r="AJ25" s="3"/>
-      <c r="AK25" s="3"/>
-      <c r="AL25" s="3"/>
+      <c r="AI25" s="16"/>
+      <c r="AJ25" s="16"/>
+      <c r="AK25" s="16"/>
+      <c r="AL25" s="16"/>
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
@@ -4010,8 +4170,12 @@
       <c r="CM25" s="3"/>
       <c r="CN25" s="3"/>
       <c r="CO25" s="3"/>
+      <c r="CP25" s="3"/>
+      <c r="CQ25" s="3"/>
+      <c r="CR25" s="3"/>
+      <c r="CS25" s="3"/>
     </row>
-    <row r="26" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B26" s="17" t="s">
         <v>22</v>
       </c>
@@ -4053,26 +4217,28 @@
       <c r="N26" s="17">
         <v>59221</v>
       </c>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17">
+      <c r="O26" s="17">
+        <v>49607</v>
+      </c>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17">
         <v>198967</v>
       </c>
-      <c r="Q26" s="17">
+      <c r="U26" s="17">
         <v>223553</v>
       </c>
-      <c r="R26" s="17">
+      <c r="V26" s="17">
         <v>236035</v>
       </c>
-      <c r="S26" s="17">
+      <c r="W26" s="17">
         <v>234478</v>
       </c>
-      <c r="T26" s="17">
+      <c r="X26" s="17">
         <v>228285</v>
       </c>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
       <c r="Y26" s="16"/>
       <c r="Z26" s="16"/>
       <c r="AA26" s="16"/>
@@ -4083,10 +4249,10 @@
       <c r="AF26" s="16"/>
       <c r="AG26" s="16"/>
       <c r="AH26" s="16"/>
-      <c r="AI26" s="3"/>
-      <c r="AJ26" s="3"/>
-      <c r="AK26" s="3"/>
-      <c r="AL26" s="3"/>
+      <c r="AI26" s="16"/>
+      <c r="AJ26" s="16"/>
+      <c r="AK26" s="16"/>
+      <c r="AL26" s="16"/>
       <c r="AM26" s="3"/>
       <c r="AN26" s="3"/>
       <c r="AO26" s="3"/>
@@ -4142,8 +4308,12 @@
       <c r="CM26" s="3"/>
       <c r="CN26" s="3"/>
       <c r="CO26" s="3"/>
+      <c r="CP26" s="3"/>
+      <c r="CQ26" s="3"/>
+      <c r="CR26" s="3"/>
+      <c r="CS26" s="3"/>
     </row>
-    <row r="27" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
         <v>23</v>
       </c>
@@ -4185,26 +4355,28 @@
       <c r="N27" s="16">
         <v>26137</v>
       </c>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16">
+      <c r="O27" s="16">
+        <v>24469</v>
+      </c>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16">
         <v>93961</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="U27" s="16">
         <v>110183</v>
       </c>
-      <c r="R27" s="16">
+      <c r="V27" s="16">
         <v>115139</v>
       </c>
-      <c r="S27" s="16">
+      <c r="W27" s="16">
         <v>109179</v>
       </c>
-      <c r="T27" s="16">
+      <c r="X27" s="16">
         <v>106464</v>
       </c>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
       <c r="Y27" s="16"/>
       <c r="Z27" s="16"/>
       <c r="AA27" s="16"/>
@@ -4215,10 +4387,10 @@
       <c r="AF27" s="16"/>
       <c r="AG27" s="16"/>
       <c r="AH27" s="16"/>
-      <c r="AI27" s="3"/>
-      <c r="AJ27" s="3"/>
-      <c r="AK27" s="3"/>
-      <c r="AL27" s="3"/>
+      <c r="AI27" s="16"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
+      <c r="AL27" s="16"/>
       <c r="AM27" s="3"/>
       <c r="AN27" s="3"/>
       <c r="AO27" s="3"/>
@@ -4274,8 +4446,12 @@
       <c r="CM27" s="3"/>
       <c r="CN27" s="3"/>
       <c r="CO27" s="3"/>
+      <c r="CP27" s="3"/>
+      <c r="CQ27" s="3"/>
+      <c r="CR27" s="3"/>
+      <c r="CS27" s="3"/>
     </row>
-    <row r="28" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B28" s="16" t="s">
         <v>24</v>
       </c>
@@ -4300,7 +4476,7 @@
         <v>27655</v>
       </c>
       <c r="H28" s="16">
-        <f t="shared" ref="H28:N28" si="4">H26-H27</f>
+        <f t="shared" ref="H28:O28" si="4">H26-H27</f>
         <v>33569</v>
       </c>
       <c r="I28" s="16">
@@ -4327,31 +4503,34 @@
         <f t="shared" si="4"/>
         <v>33084</v>
       </c>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16">
-        <f t="shared" ref="P28:Q28" si="5">P26-P27</f>
+      <c r="O28" s="16">
+        <f t="shared" si="4"/>
+        <v>25138</v>
+      </c>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16">
+        <f t="shared" ref="T28:U28" si="5">T26-T27</f>
         <v>105006</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="U28" s="16">
         <f t="shared" si="5"/>
         <v>113370</v>
       </c>
-      <c r="R28" s="16">
-        <f>R26-R27</f>
+      <c r="V28" s="16">
+        <f>V26-V27</f>
         <v>120896</v>
       </c>
-      <c r="S28" s="16">
-        <f>S26-S27</f>
+      <c r="W28" s="16">
+        <f>W26-W27</f>
         <v>125299</v>
       </c>
-      <c r="T28" s="16">
-        <f>T26-T27</f>
+      <c r="X28" s="16">
+        <f>X26-X27</f>
         <v>121821</v>
       </c>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
       <c r="Y28" s="16"/>
       <c r="Z28" s="16"/>
       <c r="AA28" s="16"/>
@@ -4362,10 +4541,10 @@
       <c r="AF28" s="16"/>
       <c r="AG28" s="16"/>
       <c r="AH28" s="16"/>
-      <c r="AI28" s="3"/>
-      <c r="AJ28" s="3"/>
-      <c r="AK28" s="3"/>
-      <c r="AL28" s="3"/>
+      <c r="AI28" s="16"/>
+      <c r="AJ28" s="16"/>
+      <c r="AK28" s="16"/>
+      <c r="AL28" s="16"/>
       <c r="AM28" s="3"/>
       <c r="AN28" s="3"/>
       <c r="AO28" s="3"/>
@@ -4421,8 +4600,12 @@
       <c r="CM28" s="3"/>
       <c r="CN28" s="3"/>
       <c r="CO28" s="3"/>
+      <c r="CP28" s="3"/>
+      <c r="CQ28" s="3"/>
+      <c r="CR28" s="3"/>
+      <c r="CS28" s="3"/>
     </row>
-    <row r="29" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B29" s="16" t="s">
         <v>25</v>
       </c>
@@ -4464,26 +4647,28 @@
       <c r="N29" s="16">
         <v>24081</v>
       </c>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16">
+      <c r="O29" s="16">
+        <v>20830</v>
+      </c>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16">
         <v>80535</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="U29" s="16">
         <v>94542</v>
       </c>
-      <c r="R29" s="16">
+      <c r="V29" s="16">
         <v>96435</v>
       </c>
-      <c r="S29" s="16">
+      <c r="W29" s="16">
         <v>97153</v>
       </c>
-      <c r="T29" s="16">
+      <c r="X29" s="16">
         <v>93023</v>
       </c>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
       <c r="Y29" s="16"/>
       <c r="Z29" s="16"/>
       <c r="AA29" s="16"/>
@@ -4494,10 +4679,10 @@
       <c r="AF29" s="16"/>
       <c r="AG29" s="16"/>
       <c r="AH29" s="16"/>
-      <c r="AI29" s="3"/>
-      <c r="AJ29" s="3"/>
-      <c r="AK29" s="3"/>
-      <c r="AL29" s="3"/>
+      <c r="AI29" s="16"/>
+      <c r="AJ29" s="16"/>
+      <c r="AK29" s="16"/>
+      <c r="AL29" s="16"/>
       <c r="AM29" s="3"/>
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
@@ -4553,8 +4738,12 @@
       <c r="CM29" s="3"/>
       <c r="CN29" s="3"/>
       <c r="CO29" s="3"/>
+      <c r="CP29" s="3"/>
+      <c r="CQ29" s="3"/>
+      <c r="CR29" s="3"/>
+      <c r="CS29" s="3"/>
     </row>
-    <row r="30" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B30" s="16" t="s">
         <v>26</v>
       </c>
@@ -4596,26 +4785,28 @@
       <c r="N30" s="16">
         <v>2617</v>
       </c>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16">
+      <c r="O30" s="16">
+        <v>2795</v>
+      </c>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16">
         <v>9216</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="U30" s="16">
         <v>11390</v>
       </c>
-      <c r="R30" s="16">
+      <c r="V30" s="16">
         <v>10895</v>
       </c>
-      <c r="S30" s="16">
+      <c r="W30" s="16">
         <v>10762</v>
       </c>
-      <c r="T30" s="16">
+      <c r="X30" s="16">
         <v>10269</v>
       </c>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
       <c r="Y30" s="16"/>
       <c r="Z30" s="16"/>
       <c r="AA30" s="16"/>
@@ -4626,10 +4817,10 @@
       <c r="AF30" s="16"/>
       <c r="AG30" s="16"/>
       <c r="AH30" s="16"/>
-      <c r="AI30" s="3"/>
-      <c r="AJ30" s="3"/>
-      <c r="AK30" s="3"/>
-      <c r="AL30" s="3"/>
+      <c r="AI30" s="16"/>
+      <c r="AJ30" s="16"/>
+      <c r="AK30" s="16"/>
+      <c r="AL30" s="16"/>
       <c r="AM30" s="3"/>
       <c r="AN30" s="3"/>
       <c r="AO30" s="3"/>
@@ -4685,8 +4876,12 @@
       <c r="CM30" s="3"/>
       <c r="CN30" s="3"/>
       <c r="CO30" s="3"/>
+      <c r="CP30" s="3"/>
+      <c r="CQ30" s="3"/>
+      <c r="CR30" s="3"/>
+      <c r="CS30" s="3"/>
     </row>
-    <row r="31" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B31" s="16" t="s">
         <v>27</v>
       </c>
@@ -4728,26 +4923,28 @@
       <c r="N31" s="16">
         <v>-22</v>
       </c>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16">
+      <c r="O31" s="23">
+        <v>-1</v>
+      </c>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16">
         <v>0</v>
       </c>
-      <c r="Q31" s="16">
+      <c r="U31" s="16">
         <v>-269</v>
       </c>
-      <c r="R31" s="16">
+      <c r="V31" s="16">
         <v>971</v>
       </c>
-      <c r="S31" s="16">
+      <c r="W31" s="16">
         <v>-78</v>
       </c>
-      <c r="T31" s="16">
+      <c r="X31" s="16">
         <v>-134</v>
       </c>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
       <c r="Y31" s="16"/>
       <c r="Z31" s="16"/>
       <c r="AA31" s="16"/>
@@ -4758,10 +4955,10 @@
       <c r="AF31" s="16"/>
       <c r="AG31" s="16"/>
       <c r="AH31" s="16"/>
-      <c r="AI31" s="3"/>
-      <c r="AJ31" s="3"/>
-      <c r="AK31" s="3"/>
-      <c r="AL31" s="3"/>
+      <c r="AI31" s="16"/>
+      <c r="AJ31" s="16"/>
+      <c r="AK31" s="16"/>
+      <c r="AL31" s="16"/>
       <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
       <c r="AO31" s="3"/>
@@ -4817,8 +5014,12 @@
       <c r="CM31" s="3"/>
       <c r="CN31" s="3"/>
       <c r="CO31" s="3"/>
+      <c r="CP31" s="3"/>
+      <c r="CQ31" s="3"/>
+      <c r="CR31" s="3"/>
+      <c r="CS31" s="3"/>
     </row>
-    <row r="32" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
         <v>28</v>
       </c>
@@ -4843,7 +5044,7 @@
         <v>2077</v>
       </c>
       <c r="H32" s="16">
-        <f t="shared" ref="H32:N32" si="7">H28-SUM(H29:H30)+H31</f>
+        <f t="shared" ref="H32:O32" si="7">H28-SUM(H29:H30)+H31</f>
         <v>7098</v>
       </c>
       <c r="I32" s="16">
@@ -4870,31 +5071,34 @@
         <f t="shared" si="7"/>
         <v>6364</v>
       </c>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16">
-        <f t="shared" ref="P32" si="8">P28-SUM(P29:P30)+P31</f>
+      <c r="O32" s="16">
+        <f t="shared" si="7"/>
+        <v>1512</v>
+      </c>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16">
+        <f t="shared" ref="T32" si="8">T28-SUM(T29:T30)+T31</f>
         <v>15255</v>
       </c>
-      <c r="Q32" s="16">
-        <f>Q28-SUM(Q29:Q30)+Q31</f>
+      <c r="U32" s="16">
+        <f>U28-SUM(U29:U30)+U31</f>
         <v>7169</v>
       </c>
-      <c r="R32" s="16">
-        <f>R28-SUM(R29:R30)+R31</f>
+      <c r="V32" s="16">
+        <f>V28-SUM(V29:V30)+V31</f>
         <v>14537</v>
       </c>
-      <c r="S32" s="16">
-        <f>S28-SUM(S29:S30)+S31</f>
+      <c r="W32" s="16">
+        <f>W28-SUM(W29:W30)+W31</f>
         <v>17306</v>
       </c>
-      <c r="T32" s="16">
-        <f>T28-SUM(T29:T30)+T31</f>
+      <c r="X32" s="16">
+        <f>X28-SUM(X29:X30)+X31</f>
         <v>18395</v>
       </c>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
       <c r="Y32" s="16"/>
       <c r="Z32" s="16"/>
       <c r="AA32" s="16"/>
@@ -4905,10 +5109,10 @@
       <c r="AF32" s="16"/>
       <c r="AG32" s="16"/>
       <c r="AH32" s="16"/>
-      <c r="AI32" s="3"/>
-      <c r="AJ32" s="3"/>
-      <c r="AK32" s="3"/>
-      <c r="AL32" s="3"/>
+      <c r="AI32" s="16"/>
+      <c r="AJ32" s="16"/>
+      <c r="AK32" s="16"/>
+      <c r="AL32" s="16"/>
       <c r="AM32" s="3"/>
       <c r="AN32" s="3"/>
       <c r="AO32" s="3"/>
@@ -4964,8 +5168,12 @@
       <c r="CM32" s="3"/>
       <c r="CN32" s="3"/>
       <c r="CO32" s="3"/>
+      <c r="CP32" s="3"/>
+      <c r="CQ32" s="3"/>
+      <c r="CR32" s="3"/>
+      <c r="CS32" s="3"/>
     </row>
-    <row r="33" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B33" s="16" t="s">
         <v>33</v>
       </c>
@@ -5008,31 +5216,33 @@
         <f>-698+161</f>
         <v>-537</v>
       </c>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16">
+      <c r="O33" s="16">
+        <v>-573</v>
+      </c>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="16">
         <f>203-1158</f>
         <v>-955</v>
       </c>
-      <c r="Q33" s="16">
+      <c r="U33" s="16">
         <f>162-1115</f>
         <v>-953</v>
       </c>
-      <c r="R33" s="16">
+      <c r="V33" s="16">
         <f>616-2143</f>
         <v>-1527</v>
       </c>
-      <c r="S33" s="16">
+      <c r="W33" s="16">
         <f>890-2753</f>
         <v>-1863</v>
       </c>
-      <c r="T33" s="16">
+      <c r="X33" s="16">
         <f>-2653+460</f>
         <v>-2193</v>
       </c>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
       <c r="Y33" s="16"/>
       <c r="Z33" s="16"/>
       <c r="AA33" s="16"/>
@@ -5043,10 +5253,10 @@
       <c r="AF33" s="16"/>
       <c r="AG33" s="16"/>
       <c r="AH33" s="16"/>
-      <c r="AI33" s="3"/>
-      <c r="AJ33" s="3"/>
-      <c r="AK33" s="3"/>
-      <c r="AL33" s="3"/>
+      <c r="AI33" s="16"/>
+      <c r="AJ33" s="16"/>
+      <c r="AK33" s="16"/>
+      <c r="AL33" s="16"/>
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
@@ -5102,8 +5312,12 @@
       <c r="CM33" s="3"/>
       <c r="CN33" s="3"/>
       <c r="CO33" s="3"/>
+      <c r="CP33" s="3"/>
+      <c r="CQ33" s="3"/>
+      <c r="CR33" s="3"/>
+      <c r="CS33" s="3"/>
     </row>
-    <row r="34" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
         <v>34</v>
       </c>
@@ -5128,7 +5342,7 @@
         <v>1606</v>
       </c>
       <c r="H34" s="16">
-        <f t="shared" ref="H34:N34" si="10">H32+H33</f>
+        <f t="shared" ref="H34:O34" si="10">H32+H33</f>
         <v>6668</v>
       </c>
       <c r="I34" s="16">
@@ -5155,31 +5369,34 @@
         <f t="shared" si="10"/>
         <v>5827</v>
       </c>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16">
-        <f t="shared" ref="P34" si="11">P32+P33</f>
+      <c r="O34" s="16">
+        <f t="shared" si="10"/>
+        <v>939</v>
+      </c>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16">
+        <f t="shared" ref="T34" si="11">T32+T33</f>
         <v>14300</v>
       </c>
-      <c r="Q34" s="16">
-        <f>Q32+Q33</f>
+      <c r="U34" s="16">
+        <f>U32+U33</f>
         <v>6216</v>
       </c>
-      <c r="R34" s="16">
-        <f t="shared" ref="R34:T34" si="12">R32+R33</f>
+      <c r="V34" s="16">
+        <f t="shared" ref="V34:X34" si="12">V32+V33</f>
         <v>13010</v>
       </c>
-      <c r="S34" s="16">
+      <c r="W34" s="16">
         <f t="shared" si="12"/>
         <v>15443</v>
       </c>
-      <c r="T34" s="16">
+      <c r="X34" s="16">
         <f t="shared" si="12"/>
         <v>16202</v>
       </c>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
       <c r="Y34" s="16"/>
       <c r="Z34" s="16"/>
       <c r="AA34" s="16"/>
@@ -5190,10 +5407,10 @@
       <c r="AF34" s="16"/>
       <c r="AG34" s="16"/>
       <c r="AH34" s="16"/>
-      <c r="AI34" s="3"/>
-      <c r="AJ34" s="3"/>
-      <c r="AK34" s="3"/>
-      <c r="AL34" s="3"/>
+      <c r="AI34" s="16"/>
+      <c r="AJ34" s="16"/>
+      <c r="AK34" s="16"/>
+      <c r="AL34" s="16"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
@@ -5249,8 +5466,12 @@
       <c r="CM34" s="3"/>
       <c r="CN34" s="3"/>
       <c r="CO34" s="3"/>
+      <c r="CP34" s="3"/>
+      <c r="CQ34" s="3"/>
+      <c r="CR34" s="3"/>
+      <c r="CS34" s="3"/>
     </row>
-    <row r="35" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
         <v>35</v>
       </c>
@@ -5292,26 +5513,28 @@
       <c r="N35" s="16">
         <v>1495</v>
       </c>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16">
+      <c r="O35" s="16">
+        <v>235</v>
+      </c>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
+      <c r="S35" s="16"/>
+      <c r="T35" s="16">
         <v>3290</v>
       </c>
-      <c r="Q35" s="16">
+      <c r="U35" s="16">
         <v>2650</v>
       </c>
-      <c r="R35" s="16">
+      <c r="V35" s="16">
         <v>4287</v>
       </c>
-      <c r="S35" s="16">
+      <c r="W35" s="16">
         <v>3859</v>
       </c>
-      <c r="T35" s="16">
+      <c r="X35" s="16">
         <v>4117</v>
       </c>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
       <c r="Y35" s="16"/>
       <c r="Z35" s="16"/>
       <c r="AA35" s="16"/>
@@ -5322,10 +5545,10 @@
       <c r="AF35" s="16"/>
       <c r="AG35" s="16"/>
       <c r="AH35" s="16"/>
-      <c r="AI35" s="3"/>
-      <c r="AJ35" s="3"/>
-      <c r="AK35" s="3"/>
-      <c r="AL35" s="3"/>
+      <c r="AI35" s="16"/>
+      <c r="AJ35" s="16"/>
+      <c r="AK35" s="16"/>
+      <c r="AL35" s="16"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
@@ -5381,8 +5604,12 @@
       <c r="CM35" s="3"/>
       <c r="CN35" s="3"/>
       <c r="CO35" s="3"/>
+      <c r="CP35" s="3"/>
+      <c r="CQ35" s="3"/>
+      <c r="CR35" s="3"/>
+      <c r="CS35" s="3"/>
     </row>
-    <row r="36" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
         <v>36</v>
       </c>
@@ -5407,7 +5634,7 @@
         <v>1201</v>
       </c>
       <c r="H36" s="16">
-        <f t="shared" ref="H36:N36" si="14">H34-H35</f>
+        <f t="shared" ref="H36:O36" si="14">H34-H35</f>
         <v>4995</v>
       </c>
       <c r="I36" s="16">
@@ -5434,31 +5661,34 @@
         <f t="shared" si="14"/>
         <v>4332</v>
       </c>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16">
-        <f>P34-P35</f>
-        <v>11010</v>
-      </c>
-      <c r="Q36" s="16">
-        <f>Q34-Q35</f>
-        <v>3566</v>
-      </c>
-      <c r="R36" s="16">
-        <f>R34-R35</f>
-        <v>8723</v>
-      </c>
-      <c r="S36" s="16">
-        <f>S34-S35</f>
-        <v>11584</v>
-      </c>
+      <c r="O36" s="16">
+        <f t="shared" si="14"/>
+        <v>704</v>
+      </c>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
       <c r="T36" s="16">
         <f>T34-T35</f>
+        <v>11010</v>
+      </c>
+      <c r="U36" s="16">
+        <f>U34-U35</f>
+        <v>3566</v>
+      </c>
+      <c r="V36" s="16">
+        <f>V34-V35</f>
+        <v>8723</v>
+      </c>
+      <c r="W36" s="16">
+        <f>W34-W35</f>
+        <v>11584</v>
+      </c>
+      <c r="X36" s="16">
+        <f>X34-X35</f>
         <v>12085</v>
       </c>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
       <c r="Y36" s="16"/>
       <c r="Z36" s="16"/>
       <c r="AA36" s="16"/>
@@ -5469,10 +5699,10 @@
       <c r="AF36" s="16"/>
       <c r="AG36" s="16"/>
       <c r="AH36" s="16"/>
-      <c r="AI36" s="3"/>
-      <c r="AJ36" s="3"/>
-      <c r="AK36" s="3"/>
-      <c r="AL36" s="3"/>
+      <c r="AI36" s="16"/>
+      <c r="AJ36" s="16"/>
+      <c r="AK36" s="16"/>
+      <c r="AL36" s="16"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
@@ -5528,8 +5758,12 @@
       <c r="CM36" s="3"/>
       <c r="CN36" s="3"/>
       <c r="CO36" s="3"/>
+      <c r="CP36" s="3"/>
+      <c r="CQ36" s="3"/>
+      <c r="CR36" s="3"/>
+      <c r="CS36" s="3"/>
     </row>
-    <row r="37" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B37" s="16" t="s">
         <v>37</v>
       </c>
@@ -5571,26 +5805,28 @@
       <c r="N37" s="16">
         <v>30</v>
       </c>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16">
+      <c r="O37" s="23">
+        <v>20</v>
+      </c>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
+      <c r="T37" s="16">
         <v>0</v>
       </c>
-      <c r="Q37" s="16">
+      <c r="U37" s="16">
         <v>0</v>
       </c>
-      <c r="R37" s="16">
+      <c r="V37" s="16">
         <v>29</v>
       </c>
-      <c r="S37" s="16">
+      <c r="W37" s="16">
         <v>37</v>
       </c>
-      <c r="T37" s="16">
+      <c r="X37" s="16">
         <v>73</v>
       </c>
-      <c r="U37" s="16"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="16"/>
-      <c r="X37" s="16"/>
       <c r="Y37" s="16"/>
       <c r="Z37" s="16"/>
       <c r="AA37" s="16"/>
@@ -5601,10 +5837,10 @@
       <c r="AF37" s="16"/>
       <c r="AG37" s="16"/>
       <c r="AH37" s="16"/>
-      <c r="AI37" s="3"/>
-      <c r="AJ37" s="3"/>
-      <c r="AK37" s="3"/>
-      <c r="AL37" s="3"/>
+      <c r="AI37" s="16"/>
+      <c r="AJ37" s="16"/>
+      <c r="AK37" s="16"/>
+      <c r="AL37" s="16"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
@@ -5660,8 +5896,12 @@
       <c r="CM37" s="3"/>
       <c r="CN37" s="3"/>
       <c r="CO37" s="3"/>
+      <c r="CP37" s="3"/>
+      <c r="CQ37" s="3"/>
+      <c r="CR37" s="3"/>
+      <c r="CS37" s="3"/>
     </row>
-    <row r="38" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B38" s="16" t="s">
         <v>38</v>
       </c>
@@ -5686,7 +5926,7 @@
         <v>1209</v>
       </c>
       <c r="H38" s="16">
-        <f t="shared" ref="H38:N38" si="16">H36+H37</f>
+        <f t="shared" ref="H38:O38" si="16">H36+H37</f>
         <v>5008</v>
       </c>
       <c r="I38" s="16">
@@ -5713,31 +5953,34 @@
         <f t="shared" si="16"/>
         <v>4362</v>
       </c>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16">
-        <f>P36+P37</f>
-        <v>11010</v>
-      </c>
-      <c r="Q38" s="16">
-        <f>Q36+Q37</f>
-        <v>3566</v>
-      </c>
-      <c r="R38" s="16">
-        <f>R36+R37</f>
-        <v>8752</v>
-      </c>
-      <c r="S38" s="16">
-        <f>S36+S37</f>
-        <v>11621</v>
-      </c>
+      <c r="O38" s="16">
+        <f t="shared" si="16"/>
+        <v>724</v>
+      </c>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
       <c r="T38" s="16">
         <f>T36+T37</f>
+        <v>11010</v>
+      </c>
+      <c r="U38" s="16">
+        <f>U36+U37</f>
+        <v>3566</v>
+      </c>
+      <c r="V38" s="16">
+        <f>V36+V37</f>
+        <v>8752</v>
+      </c>
+      <c r="W38" s="16">
+        <f>W36+W37</f>
+        <v>11621</v>
+      </c>
+      <c r="X38" s="16">
+        <f>X36+X37</f>
         <v>12158</v>
       </c>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
       <c r="Y38" s="16"/>
       <c r="Z38" s="16"/>
       <c r="AA38" s="16"/>
@@ -5748,10 +5991,10 @@
       <c r="AF38" s="16"/>
       <c r="AG38" s="16"/>
       <c r="AH38" s="16"/>
-      <c r="AI38" s="3"/>
-      <c r="AJ38" s="3"/>
-      <c r="AK38" s="3"/>
-      <c r="AL38" s="3"/>
+      <c r="AI38" s="16"/>
+      <c r="AJ38" s="16"/>
+      <c r="AK38" s="16"/>
+      <c r="AL38" s="16"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
@@ -5807,8 +6050,12 @@
       <c r="CM38" s="3"/>
       <c r="CN38" s="3"/>
       <c r="CO38" s="3"/>
+      <c r="CP38" s="3"/>
+      <c r="CQ38" s="3"/>
+      <c r="CR38" s="3"/>
+      <c r="CS38" s="3"/>
     </row>
-    <row r="39" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:97" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -5900,8 +6147,12 @@
       <c r="CM39" s="3"/>
       <c r="CN39" s="3"/>
       <c r="CO39" s="3"/>
+      <c r="CP39" s="3"/>
+      <c r="CQ39" s="3"/>
+      <c r="CR39" s="3"/>
+      <c r="CS39" s="3"/>
     </row>
-    <row r="40" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>40</v>
       </c>
@@ -5926,7 +6177,7 @@
         <v>0.74745207867721386</v>
       </c>
       <c r="H40" s="18">
-        <f t="shared" ref="H40:N40" si="18">H38/H41</f>
+        <f t="shared" ref="H40:O40" si="18">H38/H41</f>
         <v>3.1095122014824823</v>
       </c>
       <c r="I40" s="18">
@@ -5953,31 +6204,34 @@
         <f t="shared" si="18"/>
         <v>2.7205843830223557</v>
       </c>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18">
-        <f t="shared" ref="P40:Q40" si="19">P38/P41</f>
+      <c r="O40" s="18">
+        <f t="shared" si="18"/>
+        <v>0.45273881972740621</v>
+      </c>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18">
+        <f t="shared" ref="T40:U40" si="19">T38/T41</f>
         <v>6.6522785715666757</v>
       </c>
-      <c r="Q40" s="18">
+      <c r="U40" s="18">
         <f t="shared" si="19"/>
         <v>2.1614125431024815</v>
       </c>
-      <c r="R40" s="18">
-        <f>R38/R41</f>
+      <c r="V40" s="18">
+        <f>V38/V41</f>
         <v>5.3723013424001147</v>
       </c>
-      <c r="S40" s="18">
-        <f>S38/S41</f>
+      <c r="W40" s="18">
+        <f>W38/W41</f>
         <v>7.2108239922313473</v>
       </c>
-      <c r="T40" s="18">
-        <f>T38/T41</f>
+      <c r="X40" s="18">
+        <f>X38/X41</f>
         <v>7.5796445584348957</v>
       </c>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
@@ -6047,8 +6301,12 @@
       <c r="CM40" s="3"/>
       <c r="CN40" s="3"/>
       <c r="CO40" s="3"/>
+      <c r="CP40" s="3"/>
+      <c r="CQ40" s="3"/>
+      <c r="CR40" s="3"/>
+      <c r="CS40" s="3"/>
     </row>
-    <row r="41" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>39</v>
       </c>
@@ -6062,7 +6320,7 @@
         <v>1629.6869999999999</v>
       </c>
       <c r="F41" s="3">
-        <f>+R41</f>
+        <f>+V41</f>
         <v>1629.097</v>
       </c>
       <c r="G41" s="3">
@@ -6075,7 +6333,7 @@
         <v>1610.5419999999999</v>
       </c>
       <c r="J41" s="16">
-        <f>+S41</f>
+        <f>+W41</f>
         <v>1611.605</v>
       </c>
       <c r="K41" s="3">
@@ -6090,26 +6348,28 @@
       <c r="N41" s="3">
         <v>1603.3320000000001</v>
       </c>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3">
+      <c r="O41" s="3">
+        <v>1599.1559999999999</v>
+      </c>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3">
         <v>1655.0719999999999</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>1649.847</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>1629.097</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>1611.605</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>1604.0329999999999</v>
       </c>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3"/>
@@ -6179,8 +6439,12 @@
       <c r="CM41" s="3"/>
       <c r="CN41" s="3"/>
       <c r="CO41" s="3"/>
+      <c r="CP41" s="3"/>
+      <c r="CQ41" s="3"/>
+      <c r="CR41" s="3"/>
+      <c r="CS41" s="3"/>
     </row>
-    <row r="42" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:97" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -6272,8 +6536,12 @@
       <c r="CM42" s="3"/>
       <c r="CN42" s="3"/>
       <c r="CO42" s="3"/>
+      <c r="CP42" s="3"/>
+      <c r="CQ42" s="3"/>
+      <c r="CR42" s="3"/>
+      <c r="CS42" s="3"/>
     </row>
-    <row r="43" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>71</v>
       </c>
@@ -6313,33 +6581,36 @@
         <f>+N26/J26-1</f>
         <v>-4.7786728409949686E-2</v>
       </c>
-      <c r="O43" s="20"/>
+      <c r="O43" s="19">
+        <f>+O26/K26-1</f>
+        <v>-0.10348255109970539</v>
+      </c>
       <c r="P43" s="19"/>
-      <c r="Q43" s="19">
-        <f t="shared" ref="Q43" si="21">Q26/P26-1</f>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="19"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="19"/>
+      <c r="U43" s="19">
+        <f t="shared" ref="U43" si="21">U26/T26-1</f>
         <v>0.12356822990747207</v>
       </c>
-      <c r="R43" s="19">
-        <f>R26/Q26-1</f>
+      <c r="V43" s="19">
+        <f>V26/U26-1</f>
         <v>5.5834634292539098E-2</v>
       </c>
-      <c r="S43" s="19">
-        <f>S26/R26-1</f>
+      <c r="W43" s="19">
+        <f>W26/V26-1</f>
         <v>-6.5964793356917406E-3</v>
       </c>
-      <c r="T43" s="19">
-        <f>T26/S26-1</f>
+      <c r="X43" s="19">
+        <f>X26/W26-1</f>
         <v>-2.6411859534796411E-2</v>
       </c>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="20"/>
-      <c r="X43" s="20"/>
       <c r="Y43" s="20"/>
-      <c r="Z43" s="3"/>
-      <c r="AA43" s="3"/>
-      <c r="AB43" s="3"/>
-      <c r="AC43" s="3"/>
+      <c r="Z43" s="20"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
+      <c r="AC43" s="20"/>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3"/>
       <c r="AF43" s="3"/>
@@ -6404,8 +6675,12 @@
       <c r="CM43" s="3"/>
       <c r="CN43" s="3"/>
       <c r="CO43" s="3"/>
+      <c r="CP43" s="3"/>
+      <c r="CQ43" s="3"/>
+      <c r="CR43" s="3"/>
+      <c r="CS43" s="3"/>
     </row>
-    <row r="44" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>29</v>
       </c>
@@ -6454,34 +6729,37 @@
         <v>0.5286668888226318</v>
       </c>
       <c r="N44" s="21">
-        <f t="shared" ref="N44" si="25">N28/N26</f>
+        <f t="shared" ref="N44:O44" si="25">N28/N26</f>
         <v>0.5586531804596343</v>
       </c>
-      <c r="O44" s="3"/>
-      <c r="P44" s="21">
-        <f t="shared" ref="P44:Q44" si="26">P28/P26</f>
+      <c r="O44" s="21">
+        <f t="shared" si="25"/>
+        <v>0.50674299997984151</v>
+      </c>
+      <c r="P44" s="21"/>
+      <c r="Q44" s="21"/>
+      <c r="R44" s="21"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="21">
+        <f t="shared" ref="T44:U44" si="26">T28/T26</f>
         <v>0.52775585901179589</v>
       </c>
-      <c r="Q44" s="21">
+      <c r="U44" s="21">
         <f t="shared" si="26"/>
         <v>0.50712806359118423</v>
       </c>
-      <c r="R44" s="21">
-        <f>R28/R26</f>
+      <c r="V44" s="21">
+        <f>V28/V26</f>
         <v>0.51219522528438577</v>
       </c>
-      <c r="S44" s="21">
-        <f>S28/S26</f>
+      <c r="W44" s="21">
+        <f>W28/W26</f>
         <v>0.5343742270063716</v>
       </c>
-      <c r="T44" s="21">
-        <f>T28/T26</f>
+      <c r="X44" s="21">
+        <f>X28/X26</f>
         <v>0.53363558709507852</v>
       </c>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3"/>
@@ -6551,8 +6829,12 @@
       <c r="CM44" s="3"/>
       <c r="CN44" s="3"/>
       <c r="CO44" s="3"/>
+      <c r="CP44" s="3"/>
+      <c r="CQ44" s="3"/>
+      <c r="CR44" s="3"/>
+      <c r="CS44" s="3"/>
     </row>
-    <row r="45" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>30</v>
       </c>
@@ -6601,34 +6883,37 @@
         <v>8.6184822070610526E-2</v>
       </c>
       <c r="N45" s="21">
-        <f t="shared" ref="N45" si="30">N32/N26</f>
+        <f t="shared" ref="N45:O45" si="30">N32/N26</f>
         <v>0.10746188007632428</v>
       </c>
-      <c r="O45" s="3"/>
-      <c r="P45" s="21">
-        <f t="shared" ref="P45:Q45" si="31">P32/P26</f>
+      <c r="O45" s="21">
+        <f t="shared" si="30"/>
+        <v>3.0479569415606669E-2</v>
+      </c>
+      <c r="P45" s="21"/>
+      <c r="Q45" s="21"/>
+      <c r="R45" s="21"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="21">
+        <f t="shared" ref="T45:U45" si="31">T32/T26</f>
         <v>7.6671005744671228E-2</v>
       </c>
-      <c r="Q45" s="21">
+      <c r="U45" s="21">
         <f t="shared" si="31"/>
         <v>3.206845803903325E-2</v>
       </c>
-      <c r="R45" s="21">
-        <f>R32/R26</f>
+      <c r="V45" s="21">
+        <f>V32/V26</f>
         <v>6.1588323765543247E-2</v>
       </c>
-      <c r="S45" s="21">
-        <f>S32/S26</f>
+      <c r="W45" s="21">
+        <f>W32/W26</f>
         <v>7.3806497837750243E-2</v>
       </c>
-      <c r="T45" s="21">
-        <f>T32/T26</f>
+      <c r="X45" s="21">
+        <f>X32/X26</f>
         <v>8.0579100685546579E-2</v>
       </c>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
@@ -6698,8 +6983,12 @@
       <c r="CM45" s="3"/>
       <c r="CN45" s="3"/>
       <c r="CO45" s="3"/>
+      <c r="CP45" s="3"/>
+      <c r="CQ45" s="3"/>
+      <c r="CR45" s="3"/>
+      <c r="CS45" s="3"/>
     </row>
-    <row r="46" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>31</v>
       </c>
@@ -6748,34 +7037,37 @@
         <v>5.6632232492063769E-2</v>
       </c>
       <c r="N46" s="21">
-        <f t="shared" ref="N46" si="35">N38/N26</f>
+        <f t="shared" ref="N46:O46" si="35">N38/N26</f>
         <v>7.3656304351496935E-2</v>
       </c>
-      <c r="O46" s="3"/>
-      <c r="P46" s="21">
-        <f t="shared" ref="P46:Q46" si="36">P38/P26</f>
+      <c r="O46" s="21">
+        <f t="shared" si="35"/>
+        <v>1.4594714455621183E-2</v>
+      </c>
+      <c r="P46" s="21"/>
+      <c r="Q46" s="21"/>
+      <c r="R46" s="21"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="21">
+        <f t="shared" ref="T46:U46" si="36">T38/T26</f>
         <v>5.5335809455839408E-2</v>
       </c>
-      <c r="Q46" s="21">
+      <c r="U46" s="21">
         <f t="shared" si="36"/>
         <v>1.5951474594391488E-2</v>
       </c>
-      <c r="R46" s="21">
-        <f>R38/R26</f>
+      <c r="V46" s="21">
+        <f>V38/V26</f>
         <v>3.7079246721884465E-2</v>
       </c>
-      <c r="S46" s="21">
-        <f>S38/S26</f>
+      <c r="W46" s="21">
+        <f>W38/W26</f>
         <v>4.9561152858690366E-2</v>
       </c>
-      <c r="T46" s="21">
-        <f>T38/T26</f>
+      <c r="X46" s="21">
+        <f>X38/X26</f>
         <v>5.3257988917362067E-2</v>
       </c>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
@@ -6845,8 +7137,12 @@
       <c r="CM46" s="3"/>
       <c r="CN46" s="3"/>
       <c r="CO46" s="3"/>
+      <c r="CP46" s="3"/>
+      <c r="CQ46" s="3"/>
+      <c r="CR46" s="3"/>
+      <c r="CS46" s="3"/>
     </row>
-    <row r="47" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:97" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>32</v>
       </c>
@@ -6895,34 +7191,37 @@
         <v>0.25682554372975475</v>
       </c>
       <c r="N47" s="21">
-        <f t="shared" ref="N47" si="40">N35/N34</f>
+        <f t="shared" ref="N47:O47" si="40">N35/N34</f>
         <v>0.25656426977861679</v>
       </c>
-      <c r="O47" s="3"/>
-      <c r="P47" s="21">
-        <f t="shared" ref="P47:Q47" si="41">P35/P34</f>
+      <c r="O47" s="21">
+        <f t="shared" si="40"/>
+        <v>0.25026624068157616</v>
+      </c>
+      <c r="P47" s="21"/>
+      <c r="Q47" s="21"/>
+      <c r="R47" s="21"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="21">
+        <f t="shared" ref="T47:U47" si="41">T35/T34</f>
         <v>0.23006993006993007</v>
       </c>
-      <c r="Q47" s="21">
+      <c r="U47" s="21">
         <f t="shared" si="41"/>
         <v>0.42631917631917632</v>
       </c>
-      <c r="R47" s="21">
-        <f>R35/R34</f>
+      <c r="V47" s="21">
+        <f>V35/V34</f>
         <v>0.32951575710991543</v>
       </c>
-      <c r="S47" s="21">
-        <f>S35/S34</f>
+      <c r="W47" s="21">
+        <f>W35/W34</f>
         <v>0.24988668004921324</v>
       </c>
-      <c r="T47" s="21">
-        <f>T35/T34</f>
+      <c r="X47" s="21">
+        <f>X35/X34</f>
         <v>0.25410443155166029</v>
       </c>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3"/>
@@ -6992,8 +7291,12 @@
       <c r="CM47" s="3"/>
       <c r="CN47" s="3"/>
       <c r="CO47" s="3"/>
+      <c r="CP47" s="3"/>
+      <c r="CQ47" s="3"/>
+      <c r="CR47" s="3"/>
+      <c r="CS47" s="3"/>
     </row>
-    <row r="48" spans="2:93" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:97" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -7085,8 +7388,12 @@
       <c r="CM48" s="3"/>
       <c r="CN48" s="3"/>
       <c r="CO48" s="3"/>
+      <c r="CP48" s="3"/>
+      <c r="CQ48" s="3"/>
+      <c r="CR48" s="3"/>
+      <c r="CS48" s="3"/>
     </row>
-    <row r="49" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -7178,8 +7485,12 @@
       <c r="CM49" s="3"/>
       <c r="CN49" s="3"/>
       <c r="CO49" s="3"/>
+      <c r="CP49" s="3"/>
+      <c r="CQ49" s="3"/>
+      <c r="CR49" s="3"/>
+      <c r="CS49" s="3"/>
     </row>
-    <row r="50" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -7271,8 +7582,12 @@
       <c r="CM50" s="3"/>
       <c r="CN50" s="3"/>
       <c r="CO50" s="3"/>
+      <c r="CP50" s="3"/>
+      <c r="CQ50" s="3"/>
+      <c r="CR50" s="3"/>
+      <c r="CS50" s="3"/>
     </row>
-    <row r="51" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -7364,8 +7679,12 @@
       <c r="CM51" s="3"/>
       <c r="CN51" s="3"/>
       <c r="CO51" s="3"/>
+      <c r="CP51" s="3"/>
+      <c r="CQ51" s="3"/>
+      <c r="CR51" s="3"/>
+      <c r="CS51" s="3"/>
     </row>
-    <row r="52" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -7457,8 +7776,12 @@
       <c r="CM52" s="3"/>
       <c r="CN52" s="3"/>
       <c r="CO52" s="3"/>
+      <c r="CP52" s="3"/>
+      <c r="CQ52" s="3"/>
+      <c r="CR52" s="3"/>
+      <c r="CS52" s="3"/>
     </row>
-    <row r="53" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -7550,8 +7873,12 @@
       <c r="CM53" s="3"/>
       <c r="CN53" s="3"/>
       <c r="CO53" s="3"/>
+      <c r="CP53" s="3"/>
+      <c r="CQ53" s="3"/>
+      <c r="CR53" s="3"/>
+      <c r="CS53" s="3"/>
     </row>
-    <row r="54" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -7643,8 +7970,12 @@
       <c r="CM54" s="3"/>
       <c r="CN54" s="3"/>
       <c r="CO54" s="3"/>
+      <c r="CP54" s="3"/>
+      <c r="CQ54" s="3"/>
+      <c r="CR54" s="3"/>
+      <c r="CS54" s="3"/>
     </row>
-    <row r="55" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -7736,8 +8067,12 @@
       <c r="CM55" s="3"/>
       <c r="CN55" s="3"/>
       <c r="CO55" s="3"/>
+      <c r="CP55" s="3"/>
+      <c r="CQ55" s="3"/>
+      <c r="CR55" s="3"/>
+      <c r="CS55" s="3"/>
     </row>
-    <row r="56" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -7829,8 +8164,12 @@
       <c r="CM56" s="3"/>
       <c r="CN56" s="3"/>
       <c r="CO56" s="3"/>
+      <c r="CP56" s="3"/>
+      <c r="CQ56" s="3"/>
+      <c r="CR56" s="3"/>
+      <c r="CS56" s="3"/>
     </row>
-    <row r="57" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -7922,8 +8261,12 @@
       <c r="CM57" s="3"/>
       <c r="CN57" s="3"/>
       <c r="CO57" s="3"/>
+      <c r="CP57" s="3"/>
+      <c r="CQ57" s="3"/>
+      <c r="CR57" s="3"/>
+      <c r="CS57" s="3"/>
     </row>
-    <row r="58" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -8015,8 +8358,12 @@
       <c r="CM58" s="3"/>
       <c r="CN58" s="3"/>
       <c r="CO58" s="3"/>
+      <c r="CP58" s="3"/>
+      <c r="CQ58" s="3"/>
+      <c r="CR58" s="3"/>
+      <c r="CS58" s="3"/>
     </row>
-    <row r="59" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -8108,8 +8455,12 @@
       <c r="CM59" s="3"/>
       <c r="CN59" s="3"/>
       <c r="CO59" s="3"/>
+      <c r="CP59" s="3"/>
+      <c r="CQ59" s="3"/>
+      <c r="CR59" s="3"/>
+      <c r="CS59" s="3"/>
     </row>
-    <row r="60" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -8201,8 +8552,12 @@
       <c r="CM60" s="3"/>
       <c r="CN60" s="3"/>
       <c r="CO60" s="3"/>
+      <c r="CP60" s="3"/>
+      <c r="CQ60" s="3"/>
+      <c r="CR60" s="3"/>
+      <c r="CS60" s="3"/>
     </row>
-    <row r="61" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -8294,8 +8649,12 @@
       <c r="CM61" s="3"/>
       <c r="CN61" s="3"/>
       <c r="CO61" s="3"/>
+      <c r="CP61" s="3"/>
+      <c r="CQ61" s="3"/>
+      <c r="CR61" s="3"/>
+      <c r="CS61" s="3"/>
     </row>
-    <row r="62" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -8387,8 +8746,12 @@
       <c r="CM62" s="3"/>
       <c r="CN62" s="3"/>
       <c r="CO62" s="3"/>
+      <c r="CP62" s="3"/>
+      <c r="CQ62" s="3"/>
+      <c r="CR62" s="3"/>
+      <c r="CS62" s="3"/>
     </row>
-    <row r="63" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -8480,8 +8843,12 @@
       <c r="CM63" s="3"/>
       <c r="CN63" s="3"/>
       <c r="CO63" s="3"/>
+      <c r="CP63" s="3"/>
+      <c r="CQ63" s="3"/>
+      <c r="CR63" s="3"/>
+      <c r="CS63" s="3"/>
     </row>
-    <row r="64" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -8573,8 +8940,12 @@
       <c r="CM64" s="3"/>
       <c r="CN64" s="3"/>
       <c r="CO64" s="3"/>
+      <c r="CP64" s="3"/>
+      <c r="CQ64" s="3"/>
+      <c r="CR64" s="3"/>
+      <c r="CS64" s="3"/>
     </row>
-    <row r="65" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -8666,8 +9037,12 @@
       <c r="CM65" s="3"/>
       <c r="CN65" s="3"/>
       <c r="CO65" s="3"/>
+      <c r="CP65" s="3"/>
+      <c r="CQ65" s="3"/>
+      <c r="CR65" s="3"/>
+      <c r="CS65" s="3"/>
     </row>
-    <row r="66" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -8759,8 +9134,12 @@
       <c r="CM66" s="3"/>
       <c r="CN66" s="3"/>
       <c r="CO66" s="3"/>
+      <c r="CP66" s="3"/>
+      <c r="CQ66" s="3"/>
+      <c r="CR66" s="3"/>
+      <c r="CS66" s="3"/>
     </row>
-    <row r="67" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -8852,8 +9231,12 @@
       <c r="CM67" s="3"/>
       <c r="CN67" s="3"/>
       <c r="CO67" s="3"/>
+      <c r="CP67" s="3"/>
+      <c r="CQ67" s="3"/>
+      <c r="CR67" s="3"/>
+      <c r="CS67" s="3"/>
     </row>
-    <row r="68" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -8945,8 +9328,12 @@
       <c r="CM68" s="3"/>
       <c r="CN68" s="3"/>
       <c r="CO68" s="3"/>
+      <c r="CP68" s="3"/>
+      <c r="CQ68" s="3"/>
+      <c r="CR68" s="3"/>
+      <c r="CS68" s="3"/>
     </row>
-    <row r="69" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -9038,8 +9425,12 @@
       <c r="CM69" s="3"/>
       <c r="CN69" s="3"/>
       <c r="CO69" s="3"/>
+      <c r="CP69" s="3"/>
+      <c r="CQ69" s="3"/>
+      <c r="CR69" s="3"/>
+      <c r="CS69" s="3"/>
     </row>
-    <row r="70" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -9131,8 +9522,12 @@
       <c r="CM70" s="3"/>
       <c r="CN70" s="3"/>
       <c r="CO70" s="3"/>
+      <c r="CP70" s="3"/>
+      <c r="CQ70" s="3"/>
+      <c r="CR70" s="3"/>
+      <c r="CS70" s="3"/>
     </row>
-    <row r="71" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -9224,8 +9619,12 @@
       <c r="CM71" s="3"/>
       <c r="CN71" s="3"/>
       <c r="CO71" s="3"/>
+      <c r="CP71" s="3"/>
+      <c r="CQ71" s="3"/>
+      <c r="CR71" s="3"/>
+      <c r="CS71" s="3"/>
     </row>
-    <row r="72" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -9317,8 +9716,12 @@
       <c r="CM72" s="3"/>
       <c r="CN72" s="3"/>
       <c r="CO72" s="3"/>
+      <c r="CP72" s="3"/>
+      <c r="CQ72" s="3"/>
+      <c r="CR72" s="3"/>
+      <c r="CS72" s="3"/>
     </row>
-    <row r="73" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -9410,8 +9813,12 @@
       <c r="CM73" s="3"/>
       <c r="CN73" s="3"/>
       <c r="CO73" s="3"/>
+      <c r="CP73" s="3"/>
+      <c r="CQ73" s="3"/>
+      <c r="CR73" s="3"/>
+      <c r="CS73" s="3"/>
     </row>
-    <row r="74" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -9503,8 +9910,12 @@
       <c r="CM74" s="3"/>
       <c r="CN74" s="3"/>
       <c r="CO74" s="3"/>
+      <c r="CP74" s="3"/>
+      <c r="CQ74" s="3"/>
+      <c r="CR74" s="3"/>
+      <c r="CS74" s="3"/>
     </row>
-    <row r="75" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -9596,8 +10007,12 @@
       <c r="CM75" s="3"/>
       <c r="CN75" s="3"/>
       <c r="CO75" s="3"/>
+      <c r="CP75" s="3"/>
+      <c r="CQ75" s="3"/>
+      <c r="CR75" s="3"/>
+      <c r="CS75" s="3"/>
     </row>
-    <row r="76" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -9689,8 +10104,12 @@
       <c r="CM76" s="3"/>
       <c r="CN76" s="3"/>
       <c r="CO76" s="3"/>
+      <c r="CP76" s="3"/>
+      <c r="CQ76" s="3"/>
+      <c r="CR76" s="3"/>
+      <c r="CS76" s="3"/>
     </row>
-    <row r="77" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -9782,8 +10201,12 @@
       <c r="CM77" s="3"/>
       <c r="CN77" s="3"/>
       <c r="CO77" s="3"/>
+      <c r="CP77" s="3"/>
+      <c r="CQ77" s="3"/>
+      <c r="CR77" s="3"/>
+      <c r="CS77" s="3"/>
     </row>
-    <row r="78" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -9875,8 +10298,12 @@
       <c r="CM78" s="3"/>
       <c r="CN78" s="3"/>
       <c r="CO78" s="3"/>
+      <c r="CP78" s="3"/>
+      <c r="CQ78" s="3"/>
+      <c r="CR78" s="3"/>
+      <c r="CS78" s="3"/>
     </row>
-    <row r="79" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -9968,8 +10395,12 @@
       <c r="CM79" s="3"/>
       <c r="CN79" s="3"/>
       <c r="CO79" s="3"/>
+      <c r="CP79" s="3"/>
+      <c r="CQ79" s="3"/>
+      <c r="CR79" s="3"/>
+      <c r="CS79" s="3"/>
     </row>
-    <row r="80" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -10061,8 +10492,12 @@
       <c r="CM80" s="3"/>
       <c r="CN80" s="3"/>
       <c r="CO80" s="3"/>
+      <c r="CP80" s="3"/>
+      <c r="CQ80" s="3"/>
+      <c r="CR80" s="3"/>
+      <c r="CS80" s="3"/>
     </row>
-    <row r="81" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -10154,8 +10589,12 @@
       <c r="CM81" s="3"/>
       <c r="CN81" s="3"/>
       <c r="CO81" s="3"/>
+      <c r="CP81" s="3"/>
+      <c r="CQ81" s="3"/>
+      <c r="CR81" s="3"/>
+      <c r="CS81" s="3"/>
     </row>
-    <row r="82" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -10247,8 +10686,12 @@
       <c r="CM82" s="3"/>
       <c r="CN82" s="3"/>
       <c r="CO82" s="3"/>
+      <c r="CP82" s="3"/>
+      <c r="CQ82" s="3"/>
+      <c r="CR82" s="3"/>
+      <c r="CS82" s="3"/>
     </row>
-    <row r="83" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -10340,8 +10783,12 @@
       <c r="CM83" s="3"/>
       <c r="CN83" s="3"/>
       <c r="CO83" s="3"/>
+      <c r="CP83" s="3"/>
+      <c r="CQ83" s="3"/>
+      <c r="CR83" s="3"/>
+      <c r="CS83" s="3"/>
     </row>
-    <row r="84" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -10433,8 +10880,12 @@
       <c r="CM84" s="3"/>
       <c r="CN84" s="3"/>
       <c r="CO84" s="3"/>
+      <c r="CP84" s="3"/>
+      <c r="CQ84" s="3"/>
+      <c r="CR84" s="3"/>
+      <c r="CS84" s="3"/>
     </row>
-    <row r="85" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -10526,8 +10977,12 @@
       <c r="CM85" s="3"/>
       <c r="CN85" s="3"/>
       <c r="CO85" s="3"/>
+      <c r="CP85" s="3"/>
+      <c r="CQ85" s="3"/>
+      <c r="CR85" s="3"/>
+      <c r="CS85" s="3"/>
     </row>
-    <row r="86" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -10619,8 +11074,12 @@
       <c r="CM86" s="3"/>
       <c r="CN86" s="3"/>
       <c r="CO86" s="3"/>
+      <c r="CP86" s="3"/>
+      <c r="CQ86" s="3"/>
+      <c r="CR86" s="3"/>
+      <c r="CS86" s="3"/>
     </row>
-    <row r="87" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -10712,8 +11171,12 @@
       <c r="CM87" s="3"/>
       <c r="CN87" s="3"/>
       <c r="CO87" s="3"/>
+      <c r="CP87" s="3"/>
+      <c r="CQ87" s="3"/>
+      <c r="CR87" s="3"/>
+      <c r="CS87" s="3"/>
     </row>
-    <row r="88" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -10805,8 +11268,12 @@
       <c r="CM88" s="3"/>
       <c r="CN88" s="3"/>
       <c r="CO88" s="3"/>
+      <c r="CP88" s="3"/>
+      <c r="CQ88" s="3"/>
+      <c r="CR88" s="3"/>
+      <c r="CS88" s="3"/>
     </row>
-    <row r="89" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -10898,8 +11365,12 @@
       <c r="CM89" s="3"/>
       <c r="CN89" s="3"/>
       <c r="CO89" s="3"/>
+      <c r="CP89" s="3"/>
+      <c r="CQ89" s="3"/>
+      <c r="CR89" s="3"/>
+      <c r="CS89" s="3"/>
     </row>
-    <row r="90" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -10991,8 +11462,12 @@
       <c r="CM90" s="3"/>
       <c r="CN90" s="3"/>
       <c r="CO90" s="3"/>
+      <c r="CP90" s="3"/>
+      <c r="CQ90" s="3"/>
+      <c r="CR90" s="3"/>
+      <c r="CS90" s="3"/>
     </row>
-    <row r="91" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -11084,8 +11559,12 @@
       <c r="CM91" s="3"/>
       <c r="CN91" s="3"/>
       <c r="CO91" s="3"/>
+      <c r="CP91" s="3"/>
+      <c r="CQ91" s="3"/>
+      <c r="CR91" s="3"/>
+      <c r="CS91" s="3"/>
     </row>
-    <row r="92" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -11177,8 +11656,12 @@
       <c r="CM92" s="3"/>
       <c r="CN92" s="3"/>
       <c r="CO92" s="3"/>
+      <c r="CP92" s="3"/>
+      <c r="CQ92" s="3"/>
+      <c r="CR92" s="3"/>
+      <c r="CS92" s="3"/>
     </row>
-    <row r="93" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -11270,8 +11753,12 @@
       <c r="CM93" s="3"/>
       <c r="CN93" s="3"/>
       <c r="CO93" s="3"/>
+      <c r="CP93" s="3"/>
+      <c r="CQ93" s="3"/>
+      <c r="CR93" s="3"/>
+      <c r="CS93" s="3"/>
     </row>
-    <row r="94" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -11363,8 +11850,12 @@
       <c r="CM94" s="3"/>
       <c r="CN94" s="3"/>
       <c r="CO94" s="3"/>
+      <c r="CP94" s="3"/>
+      <c r="CQ94" s="3"/>
+      <c r="CR94" s="3"/>
+      <c r="CS94" s="3"/>
     </row>
-    <row r="95" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -11456,8 +11947,12 @@
       <c r="CM95" s="3"/>
       <c r="CN95" s="3"/>
       <c r="CO95" s="3"/>
+      <c r="CP95" s="3"/>
+      <c r="CQ95" s="3"/>
+      <c r="CR95" s="3"/>
+      <c r="CS95" s="3"/>
     </row>
-    <row r="96" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -11549,8 +12044,12 @@
       <c r="CM96" s="3"/>
       <c r="CN96" s="3"/>
       <c r="CO96" s="3"/>
+      <c r="CP96" s="3"/>
+      <c r="CQ96" s="3"/>
+      <c r="CR96" s="3"/>
+      <c r="CS96" s="3"/>
     </row>
-    <row r="97" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -11642,8 +12141,12 @@
       <c r="CM97" s="3"/>
       <c r="CN97" s="3"/>
       <c r="CO97" s="3"/>
+      <c r="CP97" s="3"/>
+      <c r="CQ97" s="3"/>
+      <c r="CR97" s="3"/>
+      <c r="CS97" s="3"/>
     </row>
-    <row r="98" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -11735,8 +12238,12 @@
       <c r="CM98" s="3"/>
       <c r="CN98" s="3"/>
       <c r="CO98" s="3"/>
+      <c r="CP98" s="3"/>
+      <c r="CQ98" s="3"/>
+      <c r="CR98" s="3"/>
+      <c r="CS98" s="3"/>
     </row>
-    <row r="99" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -11828,8 +12335,12 @@
       <c r="CM99" s="3"/>
       <c r="CN99" s="3"/>
       <c r="CO99" s="3"/>
+      <c r="CP99" s="3"/>
+      <c r="CQ99" s="3"/>
+      <c r="CR99" s="3"/>
+      <c r="CS99" s="3"/>
     </row>
-    <row r="100" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -11921,8 +12432,12 @@
       <c r="CM100" s="3"/>
       <c r="CN100" s="3"/>
       <c r="CO100" s="3"/>
+      <c r="CP100" s="3"/>
+      <c r="CQ100" s="3"/>
+      <c r="CR100" s="3"/>
+      <c r="CS100" s="3"/>
     </row>
-    <row r="101" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -12014,8 +12529,12 @@
       <c r="CM101" s="3"/>
       <c r="CN101" s="3"/>
       <c r="CO101" s="3"/>
+      <c r="CP101" s="3"/>
+      <c r="CQ101" s="3"/>
+      <c r="CR101" s="3"/>
+      <c r="CS101" s="3"/>
     </row>
-    <row r="102" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -12107,8 +12626,12 @@
       <c r="CM102" s="3"/>
       <c r="CN102" s="3"/>
       <c r="CO102" s="3"/>
+      <c r="CP102" s="3"/>
+      <c r="CQ102" s="3"/>
+      <c r="CR102" s="3"/>
+      <c r="CS102" s="3"/>
     </row>
-    <row r="103" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="103" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -12200,8 +12723,12 @@
       <c r="CM103" s="3"/>
       <c r="CN103" s="3"/>
       <c r="CO103" s="3"/>
+      <c r="CP103" s="3"/>
+      <c r="CQ103" s="3"/>
+      <c r="CR103" s="3"/>
+      <c r="CS103" s="3"/>
     </row>
-    <row r="104" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="104" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -12293,8 +12820,12 @@
       <c r="CM104" s="3"/>
       <c r="CN104" s="3"/>
       <c r="CO104" s="3"/>
+      <c r="CP104" s="3"/>
+      <c r="CQ104" s="3"/>
+      <c r="CR104" s="3"/>
+      <c r="CS104" s="3"/>
     </row>
-    <row r="105" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="105" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -12386,8 +12917,12 @@
       <c r="CM105" s="3"/>
       <c r="CN105" s="3"/>
       <c r="CO105" s="3"/>
+      <c r="CP105" s="3"/>
+      <c r="CQ105" s="3"/>
+      <c r="CR105" s="3"/>
+      <c r="CS105" s="3"/>
     </row>
-    <row r="106" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="106" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -12479,8 +13014,12 @@
       <c r="CM106" s="3"/>
       <c r="CN106" s="3"/>
       <c r="CO106" s="3"/>
+      <c r="CP106" s="3"/>
+      <c r="CQ106" s="3"/>
+      <c r="CR106" s="3"/>
+      <c r="CS106" s="3"/>
     </row>
-    <row r="107" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="107" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -12572,8 +13111,12 @@
       <c r="CM107" s="3"/>
       <c r="CN107" s="3"/>
       <c r="CO107" s="3"/>
+      <c r="CP107" s="3"/>
+      <c r="CQ107" s="3"/>
+      <c r="CR107" s="3"/>
+      <c r="CS107" s="3"/>
     </row>
-    <row r="108" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="108" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -12665,8 +13208,12 @@
       <c r="CM108" s="3"/>
       <c r="CN108" s="3"/>
       <c r="CO108" s="3"/>
+      <c r="CP108" s="3"/>
+      <c r="CQ108" s="3"/>
+      <c r="CR108" s="3"/>
+      <c r="CS108" s="3"/>
     </row>
-    <row r="109" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="109" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -12758,8 +13305,12 @@
       <c r="CM109" s="3"/>
       <c r="CN109" s="3"/>
       <c r="CO109" s="3"/>
+      <c r="CP109" s="3"/>
+      <c r="CQ109" s="3"/>
+      <c r="CR109" s="3"/>
+      <c r="CS109" s="3"/>
     </row>
-    <row r="110" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="110" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -12851,8 +13402,12 @@
       <c r="CM110" s="3"/>
       <c r="CN110" s="3"/>
       <c r="CO110" s="3"/>
+      <c r="CP110" s="3"/>
+      <c r="CQ110" s="3"/>
+      <c r="CR110" s="3"/>
+      <c r="CS110" s="3"/>
     </row>
-    <row r="111" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="111" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -12944,8 +13499,12 @@
       <c r="CM111" s="3"/>
       <c r="CN111" s="3"/>
       <c r="CO111" s="3"/>
+      <c r="CP111" s="3"/>
+      <c r="CQ111" s="3"/>
+      <c r="CR111" s="3"/>
+      <c r="CS111" s="3"/>
     </row>
-    <row r="112" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="112" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -13037,8 +13596,12 @@
       <c r="CM112" s="3"/>
       <c r="CN112" s="3"/>
       <c r="CO112" s="3"/>
+      <c r="CP112" s="3"/>
+      <c r="CQ112" s="3"/>
+      <c r="CR112" s="3"/>
+      <c r="CS112" s="3"/>
     </row>
-    <row r="113" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="113" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -13130,8 +13693,12 @@
       <c r="CM113" s="3"/>
       <c r="CN113" s="3"/>
       <c r="CO113" s="3"/>
+      <c r="CP113" s="3"/>
+      <c r="CQ113" s="3"/>
+      <c r="CR113" s="3"/>
+      <c r="CS113" s="3"/>
     </row>
-    <row r="114" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="114" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -13223,8 +13790,12 @@
       <c r="CM114" s="3"/>
       <c r="CN114" s="3"/>
       <c r="CO114" s="3"/>
+      <c r="CP114" s="3"/>
+      <c r="CQ114" s="3"/>
+      <c r="CR114" s="3"/>
+      <c r="CS114" s="3"/>
     </row>
-    <row r="115" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="115" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -13316,8 +13887,12 @@
       <c r="CM115" s="3"/>
       <c r="CN115" s="3"/>
       <c r="CO115" s="3"/>
+      <c r="CP115" s="3"/>
+      <c r="CQ115" s="3"/>
+      <c r="CR115" s="3"/>
+      <c r="CS115" s="3"/>
     </row>
-    <row r="116" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="116" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -13409,8 +13984,12 @@
       <c r="CM116" s="3"/>
       <c r="CN116" s="3"/>
       <c r="CO116" s="3"/>
+      <c r="CP116" s="3"/>
+      <c r="CQ116" s="3"/>
+      <c r="CR116" s="3"/>
+      <c r="CS116" s="3"/>
     </row>
-    <row r="117" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="117" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -13502,8 +14081,12 @@
       <c r="CM117" s="3"/>
       <c r="CN117" s="3"/>
       <c r="CO117" s="3"/>
+      <c r="CP117" s="3"/>
+      <c r="CQ117" s="3"/>
+      <c r="CR117" s="3"/>
+      <c r="CS117" s="3"/>
     </row>
-    <row r="118" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="118" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -13595,8 +14178,12 @@
       <c r="CM118" s="3"/>
       <c r="CN118" s="3"/>
       <c r="CO118" s="3"/>
+      <c r="CP118" s="3"/>
+      <c r="CQ118" s="3"/>
+      <c r="CR118" s="3"/>
+      <c r="CS118" s="3"/>
     </row>
-    <row r="119" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="119" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -13688,8 +14275,12 @@
       <c r="CM119" s="3"/>
       <c r="CN119" s="3"/>
       <c r="CO119" s="3"/>
+      <c r="CP119" s="3"/>
+      <c r="CQ119" s="3"/>
+      <c r="CR119" s="3"/>
+      <c r="CS119" s="3"/>
     </row>
-    <row r="120" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="120" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -13781,8 +14372,12 @@
       <c r="CM120" s="3"/>
       <c r="CN120" s="3"/>
       <c r="CO120" s="3"/>
+      <c r="CP120" s="3"/>
+      <c r="CQ120" s="3"/>
+      <c r="CR120" s="3"/>
+      <c r="CS120" s="3"/>
     </row>
-    <row r="121" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="121" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -13874,8 +14469,12 @@
       <c r="CM121" s="3"/>
       <c r="CN121" s="3"/>
       <c r="CO121" s="3"/>
+      <c r="CP121" s="3"/>
+      <c r="CQ121" s="3"/>
+      <c r="CR121" s="3"/>
+      <c r="CS121" s="3"/>
     </row>
-    <row r="122" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="122" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -13967,8 +14566,12 @@
       <c r="CM122" s="3"/>
       <c r="CN122" s="3"/>
       <c r="CO122" s="3"/>
+      <c r="CP122" s="3"/>
+      <c r="CQ122" s="3"/>
+      <c r="CR122" s="3"/>
+      <c r="CS122" s="3"/>
     </row>
-    <row r="123" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="123" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -14060,8 +14663,12 @@
       <c r="CM123" s="3"/>
       <c r="CN123" s="3"/>
       <c r="CO123" s="3"/>
+      <c r="CP123" s="3"/>
+      <c r="CQ123" s="3"/>
+      <c r="CR123" s="3"/>
+      <c r="CS123" s="3"/>
     </row>
-    <row r="124" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="124" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -14153,8 +14760,12 @@
       <c r="CM124" s="3"/>
       <c r="CN124" s="3"/>
       <c r="CO124" s="3"/>
+      <c r="CP124" s="3"/>
+      <c r="CQ124" s="3"/>
+      <c r="CR124" s="3"/>
+      <c r="CS124" s="3"/>
     </row>
-    <row r="125" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="125" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -14246,8 +14857,12 @@
       <c r="CM125" s="3"/>
       <c r="CN125" s="3"/>
       <c r="CO125" s="3"/>
+      <c r="CP125" s="3"/>
+      <c r="CQ125" s="3"/>
+      <c r="CR125" s="3"/>
+      <c r="CS125" s="3"/>
     </row>
-    <row r="126" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="126" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -14339,8 +14954,12 @@
       <c r="CM126" s="3"/>
       <c r="CN126" s="3"/>
       <c r="CO126" s="3"/>
+      <c r="CP126" s="3"/>
+      <c r="CQ126" s="3"/>
+      <c r="CR126" s="3"/>
+      <c r="CS126" s="3"/>
     </row>
-    <row r="127" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="127" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -14432,8 +15051,12 @@
       <c r="CM127" s="3"/>
       <c r="CN127" s="3"/>
       <c r="CO127" s="3"/>
+      <c r="CP127" s="3"/>
+      <c r="CQ127" s="3"/>
+      <c r="CR127" s="3"/>
+      <c r="CS127" s="3"/>
     </row>
-    <row r="128" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="128" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -14525,8 +15148,12 @@
       <c r="CM128" s="3"/>
       <c r="CN128" s="3"/>
       <c r="CO128" s="3"/>
+      <c r="CP128" s="3"/>
+      <c r="CQ128" s="3"/>
+      <c r="CR128" s="3"/>
+      <c r="CS128" s="3"/>
     </row>
-    <row r="129" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -14618,8 +15245,12 @@
       <c r="CM129" s="3"/>
       <c r="CN129" s="3"/>
       <c r="CO129" s="3"/>
+      <c r="CP129" s="3"/>
+      <c r="CQ129" s="3"/>
+      <c r="CR129" s="3"/>
+      <c r="CS129" s="3"/>
     </row>
-    <row r="130" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -14711,8 +15342,12 @@
       <c r="CM130" s="3"/>
       <c r="CN130" s="3"/>
       <c r="CO130" s="3"/>
+      <c r="CP130" s="3"/>
+      <c r="CQ130" s="3"/>
+      <c r="CR130" s="3"/>
+      <c r="CS130" s="3"/>
     </row>
-    <row r="131" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -14804,8 +15439,12 @@
       <c r="CM131" s="3"/>
       <c r="CN131" s="3"/>
       <c r="CO131" s="3"/>
+      <c r="CP131" s="3"/>
+      <c r="CQ131" s="3"/>
+      <c r="CR131" s="3"/>
+      <c r="CS131" s="3"/>
     </row>
-    <row r="132" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="132" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -14897,8 +15536,12 @@
       <c r="CM132" s="3"/>
       <c r="CN132" s="3"/>
       <c r="CO132" s="3"/>
+      <c r="CP132" s="3"/>
+      <c r="CQ132" s="3"/>
+      <c r="CR132" s="3"/>
+      <c r="CS132" s="3"/>
     </row>
-    <row r="133" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="133" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -14990,8 +15633,12 @@
       <c r="CM133" s="3"/>
       <c r="CN133" s="3"/>
       <c r="CO133" s="3"/>
+      <c r="CP133" s="3"/>
+      <c r="CQ133" s="3"/>
+      <c r="CR133" s="3"/>
+      <c r="CS133" s="3"/>
     </row>
-    <row r="134" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -15083,8 +15730,12 @@
       <c r="CM134" s="3"/>
       <c r="CN134" s="3"/>
       <c r="CO134" s="3"/>
+      <c r="CP134" s="3"/>
+      <c r="CQ134" s="3"/>
+      <c r="CR134" s="3"/>
+      <c r="CS134" s="3"/>
     </row>
-    <row r="135" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="135" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -15176,8 +15827,12 @@
       <c r="CM135" s="3"/>
       <c r="CN135" s="3"/>
       <c r="CO135" s="3"/>
+      <c r="CP135" s="3"/>
+      <c r="CQ135" s="3"/>
+      <c r="CR135" s="3"/>
+      <c r="CS135" s="3"/>
     </row>
-    <row r="136" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -15269,8 +15924,12 @@
       <c r="CM136" s="3"/>
       <c r="CN136" s="3"/>
       <c r="CO136" s="3"/>
+      <c r="CP136" s="3"/>
+      <c r="CQ136" s="3"/>
+      <c r="CR136" s="3"/>
+      <c r="CS136" s="3"/>
     </row>
-    <row r="137" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -15362,8 +16021,12 @@
       <c r="CM137" s="3"/>
       <c r="CN137" s="3"/>
       <c r="CO137" s="3"/>
+      <c r="CP137" s="3"/>
+      <c r="CQ137" s="3"/>
+      <c r="CR137" s="3"/>
+      <c r="CS137" s="3"/>
     </row>
-    <row r="138" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -15455,8 +16118,12 @@
       <c r="CM138" s="3"/>
       <c r="CN138" s="3"/>
       <c r="CO138" s="3"/>
+      <c r="CP138" s="3"/>
+      <c r="CQ138" s="3"/>
+      <c r="CR138" s="3"/>
+      <c r="CS138" s="3"/>
     </row>
-    <row r="139" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -15548,8 +16215,12 @@
       <c r="CM139" s="3"/>
       <c r="CN139" s="3"/>
       <c r="CO139" s="3"/>
+      <c r="CP139" s="3"/>
+      <c r="CQ139" s="3"/>
+      <c r="CR139" s="3"/>
+      <c r="CS139" s="3"/>
     </row>
-    <row r="140" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="140" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -15641,8 +16312,12 @@
       <c r="CM140" s="3"/>
       <c r="CN140" s="3"/>
       <c r="CO140" s="3"/>
+      <c r="CP140" s="3"/>
+      <c r="CQ140" s="3"/>
+      <c r="CR140" s="3"/>
+      <c r="CS140" s="3"/>
     </row>
-    <row r="141" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="141" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -15734,8 +16409,12 @@
       <c r="CM141" s="3"/>
       <c r="CN141" s="3"/>
       <c r="CO141" s="3"/>
+      <c r="CP141" s="3"/>
+      <c r="CQ141" s="3"/>
+      <c r="CR141" s="3"/>
+      <c r="CS141" s="3"/>
     </row>
-    <row r="142" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -15827,8 +16506,12 @@
       <c r="CM142" s="3"/>
       <c r="CN142" s="3"/>
       <c r="CO142" s="3"/>
+      <c r="CP142" s="3"/>
+      <c r="CQ142" s="3"/>
+      <c r="CR142" s="3"/>
+      <c r="CS142" s="3"/>
     </row>
-    <row r="143" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="143" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -15920,8 +16603,12 @@
       <c r="CM143" s="3"/>
       <c r="CN143" s="3"/>
       <c r="CO143" s="3"/>
+      <c r="CP143" s="3"/>
+      <c r="CQ143" s="3"/>
+      <c r="CR143" s="3"/>
+      <c r="CS143" s="3"/>
     </row>
-    <row r="144" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -16013,8 +16700,12 @@
       <c r="CM144" s="3"/>
       <c r="CN144" s="3"/>
       <c r="CO144" s="3"/>
+      <c r="CP144" s="3"/>
+      <c r="CQ144" s="3"/>
+      <c r="CR144" s="3"/>
+      <c r="CS144" s="3"/>
     </row>
-    <row r="145" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -16106,8 +16797,12 @@
       <c r="CM145" s="3"/>
       <c r="CN145" s="3"/>
       <c r="CO145" s="3"/>
+      <c r="CP145" s="3"/>
+      <c r="CQ145" s="3"/>
+      <c r="CR145" s="3"/>
+      <c r="CS145" s="3"/>
     </row>
-    <row r="146" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -16199,8 +16894,12 @@
       <c r="CM146" s="3"/>
       <c r="CN146" s="3"/>
       <c r="CO146" s="3"/>
+      <c r="CP146" s="3"/>
+      <c r="CQ146" s="3"/>
+      <c r="CR146" s="3"/>
+      <c r="CS146" s="3"/>
     </row>
-    <row r="147" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -16292,8 +16991,12 @@
       <c r="CM147" s="3"/>
       <c r="CN147" s="3"/>
       <c r="CO147" s="3"/>
+      <c r="CP147" s="3"/>
+      <c r="CQ147" s="3"/>
+      <c r="CR147" s="3"/>
+      <c r="CS147" s="3"/>
     </row>
-    <row r="148" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="148" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -16385,8 +17088,12 @@
       <c r="CM148" s="3"/>
       <c r="CN148" s="3"/>
       <c r="CO148" s="3"/>
+      <c r="CP148" s="3"/>
+      <c r="CQ148" s="3"/>
+      <c r="CR148" s="3"/>
+      <c r="CS148" s="3"/>
     </row>
-    <row r="149" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="149" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -16478,8 +17185,12 @@
       <c r="CM149" s="3"/>
       <c r="CN149" s="3"/>
       <c r="CO149" s="3"/>
+      <c r="CP149" s="3"/>
+      <c r="CQ149" s="3"/>
+      <c r="CR149" s="3"/>
+      <c r="CS149" s="3"/>
     </row>
-    <row r="150" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="150" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -16571,8 +17282,12 @@
       <c r="CM150" s="3"/>
       <c r="CN150" s="3"/>
       <c r="CO150" s="3"/>
+      <c r="CP150" s="3"/>
+      <c r="CQ150" s="3"/>
+      <c r="CR150" s="3"/>
+      <c r="CS150" s="3"/>
     </row>
-    <row r="151" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="151" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -16664,8 +17379,12 @@
       <c r="CM151" s="3"/>
       <c r="CN151" s="3"/>
       <c r="CO151" s="3"/>
+      <c r="CP151" s="3"/>
+      <c r="CQ151" s="3"/>
+      <c r="CR151" s="3"/>
+      <c r="CS151" s="3"/>
     </row>
-    <row r="152" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="152" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -16757,8 +17476,12 @@
       <c r="CM152" s="3"/>
       <c r="CN152" s="3"/>
       <c r="CO152" s="3"/>
+      <c r="CP152" s="3"/>
+      <c r="CQ152" s="3"/>
+      <c r="CR152" s="3"/>
+      <c r="CS152" s="3"/>
     </row>
-    <row r="153" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -16850,8 +17573,12 @@
       <c r="CM153" s="3"/>
       <c r="CN153" s="3"/>
       <c r="CO153" s="3"/>
+      <c r="CP153" s="3"/>
+      <c r="CQ153" s="3"/>
+      <c r="CR153" s="3"/>
+      <c r="CS153" s="3"/>
     </row>
-    <row r="154" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -16943,8 +17670,12 @@
       <c r="CM154" s="3"/>
       <c r="CN154" s="3"/>
       <c r="CO154" s="3"/>
+      <c r="CP154" s="3"/>
+      <c r="CQ154" s="3"/>
+      <c r="CR154" s="3"/>
+      <c r="CS154" s="3"/>
     </row>
-    <row r="155" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -17036,8 +17767,12 @@
       <c r="CM155" s="3"/>
       <c r="CN155" s="3"/>
       <c r="CO155" s="3"/>
+      <c r="CP155" s="3"/>
+      <c r="CQ155" s="3"/>
+      <c r="CR155" s="3"/>
+      <c r="CS155" s="3"/>
     </row>
-    <row r="156" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -17129,8 +17864,12 @@
       <c r="CM156" s="3"/>
       <c r="CN156" s="3"/>
       <c r="CO156" s="3"/>
+      <c r="CP156" s="3"/>
+      <c r="CQ156" s="3"/>
+      <c r="CR156" s="3"/>
+      <c r="CS156" s="3"/>
     </row>
-    <row r="157" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="157" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -17222,8 +17961,12 @@
       <c r="CM157" s="3"/>
       <c r="CN157" s="3"/>
       <c r="CO157" s="3"/>
+      <c r="CP157" s="3"/>
+      <c r="CQ157" s="3"/>
+      <c r="CR157" s="3"/>
+      <c r="CS157" s="3"/>
     </row>
-    <row r="158" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -17315,8 +18058,12 @@
       <c r="CM158" s="3"/>
       <c r="CN158" s="3"/>
       <c r="CO158" s="3"/>
+      <c r="CP158" s="3"/>
+      <c r="CQ158" s="3"/>
+      <c r="CR158" s="3"/>
+      <c r="CS158" s="3"/>
     </row>
-    <row r="159" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -17408,8 +18155,12 @@
       <c r="CM159" s="3"/>
       <c r="CN159" s="3"/>
       <c r="CO159" s="3"/>
+      <c r="CP159" s="3"/>
+      <c r="CQ159" s="3"/>
+      <c r="CR159" s="3"/>
+      <c r="CS159" s="3"/>
     </row>
-    <row r="160" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -17501,8 +18252,12 @@
       <c r="CM160" s="3"/>
       <c r="CN160" s="3"/>
       <c r="CO160" s="3"/>
+      <c r="CP160" s="3"/>
+      <c r="CQ160" s="3"/>
+      <c r="CR160" s="3"/>
+      <c r="CS160" s="3"/>
     </row>
-    <row r="161" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -17594,8 +18349,12 @@
       <c r="CM161" s="3"/>
       <c r="CN161" s="3"/>
       <c r="CO161" s="3"/>
+      <c r="CP161" s="3"/>
+      <c r="CQ161" s="3"/>
+      <c r="CR161" s="3"/>
+      <c r="CS161" s="3"/>
     </row>
-    <row r="162" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -17687,8 +18446,12 @@
       <c r="CM162" s="3"/>
       <c r="CN162" s="3"/>
       <c r="CO162" s="3"/>
+      <c r="CP162" s="3"/>
+      <c r="CQ162" s="3"/>
+      <c r="CR162" s="3"/>
+      <c r="CS162" s="3"/>
     </row>
-    <row r="163" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -17780,8 +18543,12 @@
       <c r="CM163" s="3"/>
       <c r="CN163" s="3"/>
       <c r="CO163" s="3"/>
+      <c r="CP163" s="3"/>
+      <c r="CQ163" s="3"/>
+      <c r="CR163" s="3"/>
+      <c r="CS163" s="3"/>
     </row>
-    <row r="164" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="164" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -17873,8 +18640,12 @@
       <c r="CM164" s="3"/>
       <c r="CN164" s="3"/>
       <c r="CO164" s="3"/>
+      <c r="CP164" s="3"/>
+      <c r="CQ164" s="3"/>
+      <c r="CR164" s="3"/>
+      <c r="CS164" s="3"/>
     </row>
-    <row r="165" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="165" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -17966,8 +18737,12 @@
       <c r="CM165" s="3"/>
       <c r="CN165" s="3"/>
       <c r="CO165" s="3"/>
+      <c r="CP165" s="3"/>
+      <c r="CQ165" s="3"/>
+      <c r="CR165" s="3"/>
+      <c r="CS165" s="3"/>
     </row>
-    <row r="166" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="166" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -18059,8 +18834,12 @@
       <c r="CM166" s="3"/>
       <c r="CN166" s="3"/>
       <c r="CO166" s="3"/>
+      <c r="CP166" s="3"/>
+      <c r="CQ166" s="3"/>
+      <c r="CR166" s="3"/>
+      <c r="CS166" s="3"/>
     </row>
-    <row r="167" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="167" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -18152,8 +18931,12 @@
       <c r="CM167" s="3"/>
       <c r="CN167" s="3"/>
       <c r="CO167" s="3"/>
+      <c r="CP167" s="3"/>
+      <c r="CQ167" s="3"/>
+      <c r="CR167" s="3"/>
+      <c r="CS167" s="3"/>
     </row>
-    <row r="168" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="168" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -18245,8 +19028,12 @@
       <c r="CM168" s="3"/>
       <c r="CN168" s="3"/>
       <c r="CO168" s="3"/>
+      <c r="CP168" s="3"/>
+      <c r="CQ168" s="3"/>
+      <c r="CR168" s="3"/>
+      <c r="CS168" s="3"/>
     </row>
-    <row r="169" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="169" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -18338,8 +19125,12 @@
       <c r="CM169" s="3"/>
       <c r="CN169" s="3"/>
       <c r="CO169" s="3"/>
+      <c r="CP169" s="3"/>
+      <c r="CQ169" s="3"/>
+      <c r="CR169" s="3"/>
+      <c r="CS169" s="3"/>
     </row>
-    <row r="170" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="170" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -18431,8 +19222,12 @@
       <c r="CM170" s="3"/>
       <c r="CN170" s="3"/>
       <c r="CO170" s="3"/>
+      <c r="CP170" s="3"/>
+      <c r="CQ170" s="3"/>
+      <c r="CR170" s="3"/>
+      <c r="CS170" s="3"/>
     </row>
-    <row r="171" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="171" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -18524,8 +19319,12 @@
       <c r="CM171" s="3"/>
       <c r="CN171" s="3"/>
       <c r="CO171" s="3"/>
+      <c r="CP171" s="3"/>
+      <c r="CQ171" s="3"/>
+      <c r="CR171" s="3"/>
+      <c r="CS171" s="3"/>
     </row>
-    <row r="172" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="172" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -18617,8 +19416,12 @@
       <c r="CM172" s="3"/>
       <c r="CN172" s="3"/>
       <c r="CO172" s="3"/>
+      <c r="CP172" s="3"/>
+      <c r="CQ172" s="3"/>
+      <c r="CR172" s="3"/>
+      <c r="CS172" s="3"/>
     </row>
-    <row r="173" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="173" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -18710,8 +19513,12 @@
       <c r="CM173" s="3"/>
       <c r="CN173" s="3"/>
       <c r="CO173" s="3"/>
+      <c r="CP173" s="3"/>
+      <c r="CQ173" s="3"/>
+      <c r="CR173" s="3"/>
+      <c r="CS173" s="3"/>
     </row>
-    <row r="174" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="174" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -18803,8 +19610,12 @@
       <c r="CM174" s="3"/>
       <c r="CN174" s="3"/>
       <c r="CO174" s="3"/>
+      <c r="CP174" s="3"/>
+      <c r="CQ174" s="3"/>
+      <c r="CR174" s="3"/>
+      <c r="CS174" s="3"/>
     </row>
-    <row r="175" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="175" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -18896,8 +19707,12 @@
       <c r="CM175" s="3"/>
       <c r="CN175" s="3"/>
       <c r="CO175" s="3"/>
+      <c r="CP175" s="3"/>
+      <c r="CQ175" s="3"/>
+      <c r="CR175" s="3"/>
+      <c r="CS175" s="3"/>
     </row>
-    <row r="176" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="176" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -18989,8 +19804,12 @@
       <c r="CM176" s="3"/>
       <c r="CN176" s="3"/>
       <c r="CO176" s="3"/>
+      <c r="CP176" s="3"/>
+      <c r="CQ176" s="3"/>
+      <c r="CR176" s="3"/>
+      <c r="CS176" s="3"/>
     </row>
-    <row r="177" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="177" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -19082,8 +19901,12 @@
       <c r="CM177" s="3"/>
       <c r="CN177" s="3"/>
       <c r="CO177" s="3"/>
+      <c r="CP177" s="3"/>
+      <c r="CQ177" s="3"/>
+      <c r="CR177" s="3"/>
+      <c r="CS177" s="3"/>
     </row>
-    <row r="178" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="178" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -19175,8 +19998,12 @@
       <c r="CM178" s="3"/>
       <c r="CN178" s="3"/>
       <c r="CO178" s="3"/>
+      <c r="CP178" s="3"/>
+      <c r="CQ178" s="3"/>
+      <c r="CR178" s="3"/>
+      <c r="CS178" s="3"/>
     </row>
-    <row r="179" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="179" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -19268,8 +20095,12 @@
       <c r="CM179" s="3"/>
       <c r="CN179" s="3"/>
       <c r="CO179" s="3"/>
+      <c r="CP179" s="3"/>
+      <c r="CQ179" s="3"/>
+      <c r="CR179" s="3"/>
+      <c r="CS179" s="3"/>
     </row>
-    <row r="180" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="180" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -19361,8 +20192,12 @@
       <c r="CM180" s="3"/>
       <c r="CN180" s="3"/>
       <c r="CO180" s="3"/>
+      <c r="CP180" s="3"/>
+      <c r="CQ180" s="3"/>
+      <c r="CR180" s="3"/>
+      <c r="CS180" s="3"/>
     </row>
-    <row r="181" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="181" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -19454,8 +20289,12 @@
       <c r="CM181" s="3"/>
       <c r="CN181" s="3"/>
       <c r="CO181" s="3"/>
+      <c r="CP181" s="3"/>
+      <c r="CQ181" s="3"/>
+      <c r="CR181" s="3"/>
+      <c r="CS181" s="3"/>
     </row>
-    <row r="182" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="182" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -19547,8 +20386,12 @@
       <c r="CM182" s="3"/>
       <c r="CN182" s="3"/>
       <c r="CO182" s="3"/>
+      <c r="CP182" s="3"/>
+      <c r="CQ182" s="3"/>
+      <c r="CR182" s="3"/>
+      <c r="CS182" s="3"/>
     </row>
-    <row r="183" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="183" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -19640,8 +20483,12 @@
       <c r="CM183" s="3"/>
       <c r="CN183" s="3"/>
       <c r="CO183" s="3"/>
+      <c r="CP183" s="3"/>
+      <c r="CQ183" s="3"/>
+      <c r="CR183" s="3"/>
+      <c r="CS183" s="3"/>
     </row>
-    <row r="184" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="184" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -19733,8 +20580,12 @@
       <c r="CM184" s="3"/>
       <c r="CN184" s="3"/>
       <c r="CO184" s="3"/>
+      <c r="CP184" s="3"/>
+      <c r="CQ184" s="3"/>
+      <c r="CR184" s="3"/>
+      <c r="CS184" s="3"/>
     </row>
-    <row r="185" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="185" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -19826,8 +20677,12 @@
       <c r="CM185" s="3"/>
       <c r="CN185" s="3"/>
       <c r="CO185" s="3"/>
+      <c r="CP185" s="3"/>
+      <c r="CQ185" s="3"/>
+      <c r="CR185" s="3"/>
+      <c r="CS185" s="3"/>
     </row>
-    <row r="186" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="186" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -19919,8 +20774,12 @@
       <c r="CM186" s="3"/>
       <c r="CN186" s="3"/>
       <c r="CO186" s="3"/>
+      <c r="CP186" s="3"/>
+      <c r="CQ186" s="3"/>
+      <c r="CR186" s="3"/>
+      <c r="CS186" s="3"/>
     </row>
-    <row r="187" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="187" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -20012,8 +20871,12 @@
       <c r="CM187" s="3"/>
       <c r="CN187" s="3"/>
       <c r="CO187" s="3"/>
+      <c r="CP187" s="3"/>
+      <c r="CQ187" s="3"/>
+      <c r="CR187" s="3"/>
+      <c r="CS187" s="3"/>
     </row>
-    <row r="188" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="188" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -20105,8 +20968,12 @@
       <c r="CM188" s="3"/>
       <c r="CN188" s="3"/>
       <c r="CO188" s="3"/>
+      <c r="CP188" s="3"/>
+      <c r="CQ188" s="3"/>
+      <c r="CR188" s="3"/>
+      <c r="CS188" s="3"/>
     </row>
-    <row r="189" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="189" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -20198,8 +21065,12 @@
       <c r="CM189" s="3"/>
       <c r="CN189" s="3"/>
       <c r="CO189" s="3"/>
+      <c r="CP189" s="3"/>
+      <c r="CQ189" s="3"/>
+      <c r="CR189" s="3"/>
+      <c r="CS189" s="3"/>
     </row>
-    <row r="190" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="190" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -20291,8 +21162,12 @@
       <c r="CM190" s="3"/>
       <c r="CN190" s="3"/>
       <c r="CO190" s="3"/>
+      <c r="CP190" s="3"/>
+      <c r="CQ190" s="3"/>
+      <c r="CR190" s="3"/>
+      <c r="CS190" s="3"/>
     </row>
-    <row r="191" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="191" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -20384,8 +21259,12 @@
       <c r="CM191" s="3"/>
       <c r="CN191" s="3"/>
       <c r="CO191" s="3"/>
+      <c r="CP191" s="3"/>
+      <c r="CQ191" s="3"/>
+      <c r="CR191" s="3"/>
+      <c r="CS191" s="3"/>
     </row>
-    <row r="192" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="192" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -20477,8 +21356,12 @@
       <c r="CM192" s="3"/>
       <c r="CN192" s="3"/>
       <c r="CO192" s="3"/>
+      <c r="CP192" s="3"/>
+      <c r="CQ192" s="3"/>
+      <c r="CR192" s="3"/>
+      <c r="CS192" s="3"/>
     </row>
-    <row r="193" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="193" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -20570,8 +21453,12 @@
       <c r="CM193" s="3"/>
       <c r="CN193" s="3"/>
       <c r="CO193" s="3"/>
+      <c r="CP193" s="3"/>
+      <c r="CQ193" s="3"/>
+      <c r="CR193" s="3"/>
+      <c r="CS193" s="3"/>
     </row>
-    <row r="194" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="194" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -20663,8 +21550,12 @@
       <c r="CM194" s="3"/>
       <c r="CN194" s="3"/>
       <c r="CO194" s="3"/>
+      <c r="CP194" s="3"/>
+      <c r="CQ194" s="3"/>
+      <c r="CR194" s="3"/>
+      <c r="CS194" s="3"/>
     </row>
-    <row r="195" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="195" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -20756,8 +21647,12 @@
       <c r="CM195" s="3"/>
       <c r="CN195" s="3"/>
       <c r="CO195" s="3"/>
+      <c r="CP195" s="3"/>
+      <c r="CQ195" s="3"/>
+      <c r="CR195" s="3"/>
+      <c r="CS195" s="3"/>
     </row>
-    <row r="196" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="196" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -20849,8 +21744,12 @@
       <c r="CM196" s="3"/>
       <c r="CN196" s="3"/>
       <c r="CO196" s="3"/>
+      <c r="CP196" s="3"/>
+      <c r="CQ196" s="3"/>
+      <c r="CR196" s="3"/>
+      <c r="CS196" s="3"/>
     </row>
-    <row r="197" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="197" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -20942,8 +21841,12 @@
       <c r="CM197" s="3"/>
       <c r="CN197" s="3"/>
       <c r="CO197" s="3"/>
+      <c r="CP197" s="3"/>
+      <c r="CQ197" s="3"/>
+      <c r="CR197" s="3"/>
+      <c r="CS197" s="3"/>
     </row>
-    <row r="198" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="198" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -21035,8 +21938,12 @@
       <c r="CM198" s="3"/>
       <c r="CN198" s="3"/>
       <c r="CO198" s="3"/>
+      <c r="CP198" s="3"/>
+      <c r="CQ198" s="3"/>
+      <c r="CR198" s="3"/>
+      <c r="CS198" s="3"/>
     </row>
-    <row r="199" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="199" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -21128,8 +22035,12 @@
       <c r="CM199" s="3"/>
       <c r="CN199" s="3"/>
       <c r="CO199" s="3"/>
+      <c r="CP199" s="3"/>
+      <c r="CQ199" s="3"/>
+      <c r="CR199" s="3"/>
+      <c r="CS199" s="3"/>
     </row>
-    <row r="200" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="200" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -21221,8 +22132,12 @@
       <c r="CM200" s="3"/>
       <c r="CN200" s="3"/>
       <c r="CO200" s="3"/>
+      <c r="CP200" s="3"/>
+      <c r="CQ200" s="3"/>
+      <c r="CR200" s="3"/>
+      <c r="CS200" s="3"/>
     </row>
-    <row r="201" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="201" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -21314,8 +22229,12 @@
       <c r="CM201" s="3"/>
       <c r="CN201" s="3"/>
       <c r="CO201" s="3"/>
+      <c r="CP201" s="3"/>
+      <c r="CQ201" s="3"/>
+      <c r="CR201" s="3"/>
+      <c r="CS201" s="3"/>
     </row>
-    <row r="202" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="202" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -21407,8 +22326,12 @@
       <c r="CM202" s="3"/>
       <c r="CN202" s="3"/>
       <c r="CO202" s="3"/>
+      <c r="CP202" s="3"/>
+      <c r="CQ202" s="3"/>
+      <c r="CR202" s="3"/>
+      <c r="CS202" s="3"/>
     </row>
-    <row r="203" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="203" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -21500,8 +22423,12 @@
       <c r="CM203" s="3"/>
       <c r="CN203" s="3"/>
       <c r="CO203" s="3"/>
+      <c r="CP203" s="3"/>
+      <c r="CQ203" s="3"/>
+      <c r="CR203" s="3"/>
+      <c r="CS203" s="3"/>
     </row>
-    <row r="204" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="204" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -21593,8 +22520,12 @@
       <c r="CM204" s="3"/>
       <c r="CN204" s="3"/>
       <c r="CO204" s="3"/>
+      <c r="CP204" s="3"/>
+      <c r="CQ204" s="3"/>
+      <c r="CR204" s="3"/>
+      <c r="CS204" s="3"/>
     </row>
-    <row r="205" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="205" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -21686,8 +22617,12 @@
       <c r="CM205" s="3"/>
       <c r="CN205" s="3"/>
       <c r="CO205" s="3"/>
+      <c r="CP205" s="3"/>
+      <c r="CQ205" s="3"/>
+      <c r="CR205" s="3"/>
+      <c r="CS205" s="3"/>
     </row>
-    <row r="206" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="206" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -21779,8 +22714,12 @@
       <c r="CM206" s="3"/>
       <c r="CN206" s="3"/>
       <c r="CO206" s="3"/>
+      <c r="CP206" s="3"/>
+      <c r="CQ206" s="3"/>
+      <c r="CR206" s="3"/>
+      <c r="CS206" s="3"/>
     </row>
-    <row r="207" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="207" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -21872,8 +22811,12 @@
       <c r="CM207" s="3"/>
       <c r="CN207" s="3"/>
       <c r="CO207" s="3"/>
+      <c r="CP207" s="3"/>
+      <c r="CQ207" s="3"/>
+      <c r="CR207" s="3"/>
+      <c r="CS207" s="3"/>
     </row>
-    <row r="208" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="208" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -21965,8 +22908,12 @@
       <c r="CM208" s="3"/>
       <c r="CN208" s="3"/>
       <c r="CO208" s="3"/>
+      <c r="CP208" s="3"/>
+      <c r="CQ208" s="3"/>
+      <c r="CR208" s="3"/>
+      <c r="CS208" s="3"/>
     </row>
-    <row r="209" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="209" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -22058,8 +23005,12 @@
       <c r="CM209" s="3"/>
       <c r="CN209" s="3"/>
       <c r="CO209" s="3"/>
+      <c r="CP209" s="3"/>
+      <c r="CQ209" s="3"/>
+      <c r="CR209" s="3"/>
+      <c r="CS209" s="3"/>
     </row>
-    <row r="210" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="210" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -22151,8 +23102,12 @@
       <c r="CM210" s="3"/>
       <c r="CN210" s="3"/>
       <c r="CO210" s="3"/>
+      <c r="CP210" s="3"/>
+      <c r="CQ210" s="3"/>
+      <c r="CR210" s="3"/>
+      <c r="CS210" s="3"/>
     </row>
-    <row r="211" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="211" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -22244,8 +23199,12 @@
       <c r="CM211" s="3"/>
       <c r="CN211" s="3"/>
       <c r="CO211" s="3"/>
+      <c r="CP211" s="3"/>
+      <c r="CQ211" s="3"/>
+      <c r="CR211" s="3"/>
+      <c r="CS211" s="3"/>
     </row>
-    <row r="212" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="212" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -22337,8 +23296,12 @@
       <c r="CM212" s="3"/>
       <c r="CN212" s="3"/>
       <c r="CO212" s="3"/>
+      <c r="CP212" s="3"/>
+      <c r="CQ212" s="3"/>
+      <c r="CR212" s="3"/>
+      <c r="CS212" s="3"/>
     </row>
-    <row r="213" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="213" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -22430,8 +23393,12 @@
       <c r="CM213" s="3"/>
       <c r="CN213" s="3"/>
       <c r="CO213" s="3"/>
+      <c r="CP213" s="3"/>
+      <c r="CQ213" s="3"/>
+      <c r="CR213" s="3"/>
+      <c r="CS213" s="3"/>
     </row>
-    <row r="214" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="214" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -22523,8 +23490,12 @@
       <c r="CM214" s="3"/>
       <c r="CN214" s="3"/>
       <c r="CO214" s="3"/>
+      <c r="CP214" s="3"/>
+      <c r="CQ214" s="3"/>
+      <c r="CR214" s="3"/>
+      <c r="CS214" s="3"/>
     </row>
-    <row r="215" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="215" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -22616,8 +23587,12 @@
       <c r="CM215" s="3"/>
       <c r="CN215" s="3"/>
       <c r="CO215" s="3"/>
+      <c r="CP215" s="3"/>
+      <c r="CQ215" s="3"/>
+      <c r="CR215" s="3"/>
+      <c r="CS215" s="3"/>
     </row>
-    <row r="216" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="216" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -22709,8 +23684,12 @@
       <c r="CM216" s="3"/>
       <c r="CN216" s="3"/>
       <c r="CO216" s="3"/>
+      <c r="CP216" s="3"/>
+      <c r="CQ216" s="3"/>
+      <c r="CR216" s="3"/>
+      <c r="CS216" s="3"/>
     </row>
-    <row r="217" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="217" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -22802,8 +23781,12 @@
       <c r="CM217" s="3"/>
       <c r="CN217" s="3"/>
       <c r="CO217" s="3"/>
+      <c r="CP217" s="3"/>
+      <c r="CQ217" s="3"/>
+      <c r="CR217" s="3"/>
+      <c r="CS217" s="3"/>
     </row>
-    <row r="218" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="218" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -22895,8 +23878,12 @@
       <c r="CM218" s="3"/>
       <c r="CN218" s="3"/>
       <c r="CO218" s="3"/>
+      <c r="CP218" s="3"/>
+      <c r="CQ218" s="3"/>
+      <c r="CR218" s="3"/>
+      <c r="CS218" s="3"/>
     </row>
-    <row r="219" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="219" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -22988,8 +23975,12 @@
       <c r="CM219" s="3"/>
       <c r="CN219" s="3"/>
       <c r="CO219" s="3"/>
+      <c r="CP219" s="3"/>
+      <c r="CQ219" s="3"/>
+      <c r="CR219" s="3"/>
+      <c r="CS219" s="3"/>
     </row>
-    <row r="220" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="220" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -23081,8 +24072,12 @@
       <c r="CM220" s="3"/>
       <c r="CN220" s="3"/>
       <c r="CO220" s="3"/>
+      <c r="CP220" s="3"/>
+      <c r="CQ220" s="3"/>
+      <c r="CR220" s="3"/>
+      <c r="CS220" s="3"/>
     </row>
-    <row r="221" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="221" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -23174,8 +24169,12 @@
       <c r="CM221" s="3"/>
       <c r="CN221" s="3"/>
       <c r="CO221" s="3"/>
+      <c r="CP221" s="3"/>
+      <c r="CQ221" s="3"/>
+      <c r="CR221" s="3"/>
+      <c r="CS221" s="3"/>
     </row>
-    <row r="222" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="222" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -23267,8 +24266,12 @@
       <c r="CM222" s="3"/>
       <c r="CN222" s="3"/>
       <c r="CO222" s="3"/>
+      <c r="CP222" s="3"/>
+      <c r="CQ222" s="3"/>
+      <c r="CR222" s="3"/>
+      <c r="CS222" s="3"/>
     </row>
-    <row r="223" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="223" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -23360,8 +24363,12 @@
       <c r="CM223" s="3"/>
       <c r="CN223" s="3"/>
       <c r="CO223" s="3"/>
+      <c r="CP223" s="3"/>
+      <c r="CQ223" s="3"/>
+      <c r="CR223" s="3"/>
+      <c r="CS223" s="3"/>
     </row>
-    <row r="224" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="224" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -23453,8 +24460,12 @@
       <c r="CM224" s="3"/>
       <c r="CN224" s="3"/>
       <c r="CO224" s="3"/>
+      <c r="CP224" s="3"/>
+      <c r="CQ224" s="3"/>
+      <c r="CR224" s="3"/>
+      <c r="CS224" s="3"/>
     </row>
-    <row r="225" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="225" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -23546,8 +24557,12 @@
       <c r="CM225" s="3"/>
       <c r="CN225" s="3"/>
       <c r="CO225" s="3"/>
+      <c r="CP225" s="3"/>
+      <c r="CQ225" s="3"/>
+      <c r="CR225" s="3"/>
+      <c r="CS225" s="3"/>
     </row>
-    <row r="226" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="226" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -23639,8 +24654,12 @@
       <c r="CM226" s="3"/>
       <c r="CN226" s="3"/>
       <c r="CO226" s="3"/>
+      <c r="CP226" s="3"/>
+      <c r="CQ226" s="3"/>
+      <c r="CR226" s="3"/>
+      <c r="CS226" s="3"/>
     </row>
-    <row r="227" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="227" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -23732,8 +24751,12 @@
       <c r="CM227" s="3"/>
       <c r="CN227" s="3"/>
       <c r="CO227" s="3"/>
+      <c r="CP227" s="3"/>
+      <c r="CQ227" s="3"/>
+      <c r="CR227" s="3"/>
+      <c r="CS227" s="3"/>
     </row>
-    <row r="228" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="228" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -23825,8 +24848,12 @@
       <c r="CM228" s="3"/>
       <c r="CN228" s="3"/>
       <c r="CO228" s="3"/>
+      <c r="CP228" s="3"/>
+      <c r="CQ228" s="3"/>
+      <c r="CR228" s="3"/>
+      <c r="CS228" s="3"/>
     </row>
-    <row r="229" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="229" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -23918,8 +24945,12 @@
       <c r="CM229" s="3"/>
       <c r="CN229" s="3"/>
       <c r="CO229" s="3"/>
+      <c r="CP229" s="3"/>
+      <c r="CQ229" s="3"/>
+      <c r="CR229" s="3"/>
+      <c r="CS229" s="3"/>
     </row>
-    <row r="230" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="230" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -24011,8 +25042,12 @@
       <c r="CM230" s="3"/>
       <c r="CN230" s="3"/>
       <c r="CO230" s="3"/>
+      <c r="CP230" s="3"/>
+      <c r="CQ230" s="3"/>
+      <c r="CR230" s="3"/>
+      <c r="CS230" s="3"/>
     </row>
-    <row r="231" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="231" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -24104,8 +25139,12 @@
       <c r="CM231" s="3"/>
       <c r="CN231" s="3"/>
       <c r="CO231" s="3"/>
+      <c r="CP231" s="3"/>
+      <c r="CQ231" s="3"/>
+      <c r="CR231" s="3"/>
+      <c r="CS231" s="3"/>
     </row>
-    <row r="232" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="232" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -24197,8 +25236,12 @@
       <c r="CM232" s="3"/>
       <c r="CN232" s="3"/>
       <c r="CO232" s="3"/>
+      <c r="CP232" s="3"/>
+      <c r="CQ232" s="3"/>
+      <c r="CR232" s="3"/>
+      <c r="CS232" s="3"/>
     </row>
-    <row r="233" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="233" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -24290,8 +25333,12 @@
       <c r="CM233" s="3"/>
       <c r="CN233" s="3"/>
       <c r="CO233" s="3"/>
+      <c r="CP233" s="3"/>
+      <c r="CQ233" s="3"/>
+      <c r="CR233" s="3"/>
+      <c r="CS233" s="3"/>
     </row>
-    <row r="234" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="234" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -24383,8 +25430,12 @@
       <c r="CM234" s="3"/>
       <c r="CN234" s="3"/>
       <c r="CO234" s="3"/>
+      <c r="CP234" s="3"/>
+      <c r="CQ234" s="3"/>
+      <c r="CR234" s="3"/>
+      <c r="CS234" s="3"/>
     </row>
-    <row r="235" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="235" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -24476,8 +25527,12 @@
       <c r="CM235" s="3"/>
       <c r="CN235" s="3"/>
       <c r="CO235" s="3"/>
+      <c r="CP235" s="3"/>
+      <c r="CQ235" s="3"/>
+      <c r="CR235" s="3"/>
+      <c r="CS235" s="3"/>
     </row>
-    <row r="236" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="236" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -24569,8 +25624,12 @@
       <c r="CM236" s="3"/>
       <c r="CN236" s="3"/>
       <c r="CO236" s="3"/>
+      <c r="CP236" s="3"/>
+      <c r="CQ236" s="3"/>
+      <c r="CR236" s="3"/>
+      <c r="CS236" s="3"/>
     </row>
-    <row r="237" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="237" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -24662,8 +25721,12 @@
       <c r="CM237" s="3"/>
       <c r="CN237" s="3"/>
       <c r="CO237" s="3"/>
+      <c r="CP237" s="3"/>
+      <c r="CQ237" s="3"/>
+      <c r="CR237" s="3"/>
+      <c r="CS237" s="3"/>
     </row>
-    <row r="238" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="238" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -24755,8 +25818,12 @@
       <c r="CM238" s="3"/>
       <c r="CN238" s="3"/>
       <c r="CO238" s="3"/>
+      <c r="CP238" s="3"/>
+      <c r="CQ238" s="3"/>
+      <c r="CR238" s="3"/>
+      <c r="CS238" s="3"/>
     </row>
-    <row r="239" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="239" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -24848,8 +25915,12 @@
       <c r="CM239" s="3"/>
       <c r="CN239" s="3"/>
       <c r="CO239" s="3"/>
+      <c r="CP239" s="3"/>
+      <c r="CQ239" s="3"/>
+      <c r="CR239" s="3"/>
+      <c r="CS239" s="3"/>
     </row>
-    <row r="240" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="240" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -24941,8 +26012,12 @@
       <c r="CM240" s="3"/>
       <c r="CN240" s="3"/>
       <c r="CO240" s="3"/>
+      <c r="CP240" s="3"/>
+      <c r="CQ240" s="3"/>
+      <c r="CR240" s="3"/>
+      <c r="CS240" s="3"/>
     </row>
-    <row r="241" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="241" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -25034,8 +26109,12 @@
       <c r="CM241" s="3"/>
       <c r="CN241" s="3"/>
       <c r="CO241" s="3"/>
+      <c r="CP241" s="3"/>
+      <c r="CQ241" s="3"/>
+      <c r="CR241" s="3"/>
+      <c r="CS241" s="3"/>
     </row>
-    <row r="242" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="242" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -25127,8 +26206,12 @@
       <c r="CM242" s="3"/>
       <c r="CN242" s="3"/>
       <c r="CO242" s="3"/>
+      <c r="CP242" s="3"/>
+      <c r="CQ242" s="3"/>
+      <c r="CR242" s="3"/>
+      <c r="CS242" s="3"/>
     </row>
-    <row r="243" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="243" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -25220,8 +26303,12 @@
       <c r="CM243" s="3"/>
       <c r="CN243" s="3"/>
       <c r="CO243" s="3"/>
+      <c r="CP243" s="3"/>
+      <c r="CQ243" s="3"/>
+      <c r="CR243" s="3"/>
+      <c r="CS243" s="3"/>
     </row>
-    <row r="244" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="244" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -25313,8 +26400,12 @@
       <c r="CM244" s="3"/>
       <c r="CN244" s="3"/>
       <c r="CO244" s="3"/>
+      <c r="CP244" s="3"/>
+      <c r="CQ244" s="3"/>
+      <c r="CR244" s="3"/>
+      <c r="CS244" s="3"/>
     </row>
-    <row r="245" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="245" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -25406,8 +26497,12 @@
       <c r="CM245" s="3"/>
       <c r="CN245" s="3"/>
       <c r="CO245" s="3"/>
+      <c r="CP245" s="3"/>
+      <c r="CQ245" s="3"/>
+      <c r="CR245" s="3"/>
+      <c r="CS245" s="3"/>
     </row>
-    <row r="246" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="246" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -25499,8 +26594,12 @@
       <c r="CM246" s="3"/>
       <c r="CN246" s="3"/>
       <c r="CO246" s="3"/>
+      <c r="CP246" s="3"/>
+      <c r="CQ246" s="3"/>
+      <c r="CR246" s="3"/>
+      <c r="CS246" s="3"/>
     </row>
-    <row r="247" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="247" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -25592,8 +26691,12 @@
       <c r="CM247" s="3"/>
       <c r="CN247" s="3"/>
       <c r="CO247" s="3"/>
+      <c r="CP247" s="3"/>
+      <c r="CQ247" s="3"/>
+      <c r="CR247" s="3"/>
+      <c r="CS247" s="3"/>
     </row>
-    <row r="248" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="248" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -25685,8 +26788,12 @@
       <c r="CM248" s="3"/>
       <c r="CN248" s="3"/>
       <c r="CO248" s="3"/>
+      <c r="CP248" s="3"/>
+      <c r="CQ248" s="3"/>
+      <c r="CR248" s="3"/>
+      <c r="CS248" s="3"/>
     </row>
-    <row r="249" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="249" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -25778,8 +26885,12 @@
       <c r="CM249" s="3"/>
       <c r="CN249" s="3"/>
       <c r="CO249" s="3"/>
+      <c r="CP249" s="3"/>
+      <c r="CQ249" s="3"/>
+      <c r="CR249" s="3"/>
+      <c r="CS249" s="3"/>
     </row>
-    <row r="250" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="250" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -25871,8 +26982,12 @@
       <c r="CM250" s="3"/>
       <c r="CN250" s="3"/>
       <c r="CO250" s="3"/>
+      <c r="CP250" s="3"/>
+      <c r="CQ250" s="3"/>
+      <c r="CR250" s="3"/>
+      <c r="CS250" s="3"/>
     </row>
-    <row r="251" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="251" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -25964,8 +27079,12 @@
       <c r="CM251" s="3"/>
       <c r="CN251" s="3"/>
       <c r="CO251" s="3"/>
+      <c r="CP251" s="3"/>
+      <c r="CQ251" s="3"/>
+      <c r="CR251" s="3"/>
+      <c r="CS251" s="3"/>
     </row>
-    <row r="252" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="252" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -26057,8 +27176,12 @@
       <c r="CM252" s="3"/>
       <c r="CN252" s="3"/>
       <c r="CO252" s="3"/>
+      <c r="CP252" s="3"/>
+      <c r="CQ252" s="3"/>
+      <c r="CR252" s="3"/>
+      <c r="CS252" s="3"/>
     </row>
-    <row r="253" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="253" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -26150,8 +27273,12 @@
       <c r="CM253" s="3"/>
       <c r="CN253" s="3"/>
       <c r="CO253" s="3"/>
+      <c r="CP253" s="3"/>
+      <c r="CQ253" s="3"/>
+      <c r="CR253" s="3"/>
+      <c r="CS253" s="3"/>
     </row>
-    <row r="254" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="254" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -26243,8 +27370,12 @@
       <c r="CM254" s="3"/>
       <c r="CN254" s="3"/>
       <c r="CO254" s="3"/>
+      <c r="CP254" s="3"/>
+      <c r="CQ254" s="3"/>
+      <c r="CR254" s="3"/>
+      <c r="CS254" s="3"/>
     </row>
-    <row r="255" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="255" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -26336,8 +27467,12 @@
       <c r="CM255" s="3"/>
       <c r="CN255" s="3"/>
       <c r="CO255" s="3"/>
+      <c r="CP255" s="3"/>
+      <c r="CQ255" s="3"/>
+      <c r="CR255" s="3"/>
+      <c r="CS255" s="3"/>
     </row>
-    <row r="256" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="256" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -26429,8 +27564,12 @@
       <c r="CM256" s="3"/>
       <c r="CN256" s="3"/>
       <c r="CO256" s="3"/>
+      <c r="CP256" s="3"/>
+      <c r="CQ256" s="3"/>
+      <c r="CR256" s="3"/>
+      <c r="CS256" s="3"/>
     </row>
-    <row r="257" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="257" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -26522,8 +27661,12 @@
       <c r="CM257" s="3"/>
       <c r="CN257" s="3"/>
       <c r="CO257" s="3"/>
+      <c r="CP257" s="3"/>
+      <c r="CQ257" s="3"/>
+      <c r="CR257" s="3"/>
+      <c r="CS257" s="3"/>
     </row>
-    <row r="258" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="258" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -26615,8 +27758,12 @@
       <c r="CM258" s="3"/>
       <c r="CN258" s="3"/>
       <c r="CO258" s="3"/>
+      <c r="CP258" s="3"/>
+      <c r="CQ258" s="3"/>
+      <c r="CR258" s="3"/>
+      <c r="CS258" s="3"/>
     </row>
-    <row r="259" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="259" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -26708,8 +27855,12 @@
       <c r="CM259" s="3"/>
       <c r="CN259" s="3"/>
       <c r="CO259" s="3"/>
+      <c r="CP259" s="3"/>
+      <c r="CQ259" s="3"/>
+      <c r="CR259" s="3"/>
+      <c r="CS259" s="3"/>
     </row>
-    <row r="260" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="260" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -26801,8 +27952,12 @@
       <c r="CM260" s="3"/>
       <c r="CN260" s="3"/>
       <c r="CO260" s="3"/>
+      <c r="CP260" s="3"/>
+      <c r="CQ260" s="3"/>
+      <c r="CR260" s="3"/>
+      <c r="CS260" s="3"/>
     </row>
-    <row r="261" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="261" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -26894,8 +28049,12 @@
       <c r="CM261" s="3"/>
       <c r="CN261" s="3"/>
       <c r="CO261" s="3"/>
+      <c r="CP261" s="3"/>
+      <c r="CQ261" s="3"/>
+      <c r="CR261" s="3"/>
+      <c r="CS261" s="3"/>
     </row>
-    <row r="262" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="262" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -26987,8 +28146,12 @@
       <c r="CM262" s="3"/>
       <c r="CN262" s="3"/>
       <c r="CO262" s="3"/>
+      <c r="CP262" s="3"/>
+      <c r="CQ262" s="3"/>
+      <c r="CR262" s="3"/>
+      <c r="CS262" s="3"/>
     </row>
-    <row r="263" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="263" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -27080,8 +28243,12 @@
       <c r="CM263" s="3"/>
       <c r="CN263" s="3"/>
       <c r="CO263" s="3"/>
+      <c r="CP263" s="3"/>
+      <c r="CQ263" s="3"/>
+      <c r="CR263" s="3"/>
+      <c r="CS263" s="3"/>
     </row>
-    <row r="264" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="264" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -27173,8 +28340,12 @@
       <c r="CM264" s="3"/>
       <c r="CN264" s="3"/>
       <c r="CO264" s="3"/>
+      <c r="CP264" s="3"/>
+      <c r="CQ264" s="3"/>
+      <c r="CR264" s="3"/>
+      <c r="CS264" s="3"/>
     </row>
-    <row r="265" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="265" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -27266,8 +28437,12 @@
       <c r="CM265" s="3"/>
       <c r="CN265" s="3"/>
       <c r="CO265" s="3"/>
+      <c r="CP265" s="3"/>
+      <c r="CQ265" s="3"/>
+      <c r="CR265" s="3"/>
+      <c r="CS265" s="3"/>
     </row>
-    <row r="266" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="266" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -27359,8 +28534,12 @@
       <c r="CM266" s="3"/>
       <c r="CN266" s="3"/>
       <c r="CO266" s="3"/>
+      <c r="CP266" s="3"/>
+      <c r="CQ266" s="3"/>
+      <c r="CR266" s="3"/>
+      <c r="CS266" s="3"/>
     </row>
-    <row r="267" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="267" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -27452,8 +28631,12 @@
       <c r="CM267" s="3"/>
       <c r="CN267" s="3"/>
       <c r="CO267" s="3"/>
+      <c r="CP267" s="3"/>
+      <c r="CQ267" s="3"/>
+      <c r="CR267" s="3"/>
+      <c r="CS267" s="3"/>
     </row>
-    <row r="268" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="268" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -27545,8 +28728,12 @@
       <c r="CM268" s="3"/>
       <c r="CN268" s="3"/>
       <c r="CO268" s="3"/>
+      <c r="CP268" s="3"/>
+      <c r="CQ268" s="3"/>
+      <c r="CR268" s="3"/>
+      <c r="CS268" s="3"/>
     </row>
-    <row r="269" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="269" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -27638,8 +28825,12 @@
       <c r="CM269" s="3"/>
       <c r="CN269" s="3"/>
       <c r="CO269" s="3"/>
+      <c r="CP269" s="3"/>
+      <c r="CQ269" s="3"/>
+      <c r="CR269" s="3"/>
+      <c r="CS269" s="3"/>
     </row>
-    <row r="270" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="270" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -27731,8 +28922,12 @@
       <c r="CM270" s="3"/>
       <c r="CN270" s="3"/>
       <c r="CO270" s="3"/>
+      <c r="CP270" s="3"/>
+      <c r="CQ270" s="3"/>
+      <c r="CR270" s="3"/>
+      <c r="CS270" s="3"/>
     </row>
-    <row r="271" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="271" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -27824,8 +29019,12 @@
       <c r="CM271" s="3"/>
       <c r="CN271" s="3"/>
       <c r="CO271" s="3"/>
+      <c r="CP271" s="3"/>
+      <c r="CQ271" s="3"/>
+      <c r="CR271" s="3"/>
+      <c r="CS271" s="3"/>
     </row>
-    <row r="272" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="272" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -27917,8 +29116,12 @@
       <c r="CM272" s="3"/>
       <c r="CN272" s="3"/>
       <c r="CO272" s="3"/>
+      <c r="CP272" s="3"/>
+      <c r="CQ272" s="3"/>
+      <c r="CR272" s="3"/>
+      <c r="CS272" s="3"/>
     </row>
-    <row r="273" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="273" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -28010,8 +29213,12 @@
       <c r="CM273" s="3"/>
       <c r="CN273" s="3"/>
       <c r="CO273" s="3"/>
+      <c r="CP273" s="3"/>
+      <c r="CQ273" s="3"/>
+      <c r="CR273" s="3"/>
+      <c r="CS273" s="3"/>
     </row>
-    <row r="274" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="274" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -28103,8 +29310,12 @@
       <c r="CM274" s="3"/>
       <c r="CN274" s="3"/>
       <c r="CO274" s="3"/>
+      <c r="CP274" s="3"/>
+      <c r="CQ274" s="3"/>
+      <c r="CR274" s="3"/>
+      <c r="CS274" s="3"/>
     </row>
-    <row r="275" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="275" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -28196,8 +29407,12 @@
       <c r="CM275" s="3"/>
       <c r="CN275" s="3"/>
       <c r="CO275" s="3"/>
+      <c r="CP275" s="3"/>
+      <c r="CQ275" s="3"/>
+      <c r="CR275" s="3"/>
+      <c r="CS275" s="3"/>
     </row>
-    <row r="276" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="276" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -28289,8 +29504,12 @@
       <c r="CM276" s="3"/>
       <c r="CN276" s="3"/>
       <c r="CO276" s="3"/>
+      <c r="CP276" s="3"/>
+      <c r="CQ276" s="3"/>
+      <c r="CR276" s="3"/>
+      <c r="CS276" s="3"/>
     </row>
-    <row r="277" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="277" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -28382,8 +29601,12 @@
       <c r="CM277" s="3"/>
       <c r="CN277" s="3"/>
       <c r="CO277" s="3"/>
+      <c r="CP277" s="3"/>
+      <c r="CQ277" s="3"/>
+      <c r="CR277" s="3"/>
+      <c r="CS277" s="3"/>
     </row>
-    <row r="278" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="278" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -28475,8 +29698,12 @@
       <c r="CM278" s="3"/>
       <c r="CN278" s="3"/>
       <c r="CO278" s="3"/>
+      <c r="CP278" s="3"/>
+      <c r="CQ278" s="3"/>
+      <c r="CR278" s="3"/>
+      <c r="CS278" s="3"/>
     </row>
-    <row r="279" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="279" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -28568,8 +29795,12 @@
       <c r="CM279" s="3"/>
       <c r="CN279" s="3"/>
       <c r="CO279" s="3"/>
+      <c r="CP279" s="3"/>
+      <c r="CQ279" s="3"/>
+      <c r="CR279" s="3"/>
+      <c r="CS279" s="3"/>
     </row>
-    <row r="280" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="280" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -28661,8 +29892,12 @@
       <c r="CM280" s="3"/>
       <c r="CN280" s="3"/>
       <c r="CO280" s="3"/>
+      <c r="CP280" s="3"/>
+      <c r="CQ280" s="3"/>
+      <c r="CR280" s="3"/>
+      <c r="CS280" s="3"/>
     </row>
-    <row r="281" spans="3:93" x14ac:dyDescent="0.2">
+    <row r="281" spans="3:97" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -28754,6 +29989,10 @@
       <c r="CM281" s="3"/>
       <c r="CN281" s="3"/>
       <c r="CO281" s="3"/>
+      <c r="CP281" s="3"/>
+      <c r="CQ281" s="3"/>
+      <c r="CR281" s="3"/>
+      <c r="CS281" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/HM.BST.xlsx
+++ b/HM.BST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BCD860-0583-47A2-93A6-19BBB0D55174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37697899-236B-4999-B371-486648B82E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{A344954E-3009-47EB-94FE-5B6CEBCD1700}"/>
   </bookViews>
@@ -280,13 +280,19 @@
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;[Red]#,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -443,38 +449,41 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -894,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="2">
-        <v>170.3</v>
+        <v>166.25</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -902,10 +911,10 @@
         <v>11</v>
       </c>
       <c r="I3" s="3">
-        <v>1599.1559999999999</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>73</v>
+        <v>1597.6010000000001</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -917,7 +926,7 @@
       </c>
       <c r="I4" s="6">
         <f>I3*I2</f>
-        <v>272336.26679999998</v>
+        <v>265601.16625000001</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -929,10 +938,10 @@
         <v>13</v>
       </c>
       <c r="I5" s="6">
-        <v>18733</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>73</v>
+        <v>18697</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -943,8 +952,8 @@
         <f>18330+2345</f>
         <v>20675</v>
       </c>
-      <c r="J6" s="22" t="s">
-        <v>73</v>
+      <c r="J6" s="24" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -956,7 +965,7 @@
       </c>
       <c r="I7" s="6">
         <f>I4+I6-I5</f>
-        <v>274278.26679999998</v>
+        <v>267579.16625000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1135,7 +1144,9 @@
       <c r="O3" s="16">
         <v>3616</v>
       </c>
-      <c r="P3" s="16"/>
+      <c r="P3" s="16">
+        <v>3599</v>
+      </c>
       <c r="Q3" s="16"/>
       <c r="R3" s="16"/>
       <c r="S3" s="16"/>
@@ -1271,7 +1282,9 @@
       <c r="O4" s="16">
         <v>247</v>
       </c>
-      <c r="P4" s="16"/>
+      <c r="P4" s="16">
+        <v>252</v>
+      </c>
       <c r="Q4" s="16"/>
       <c r="R4" s="16"/>
       <c r="S4" s="16"/>
@@ -1407,7 +1420,9 @@
       <c r="O5" s="16">
         <v>0</v>
       </c>
-      <c r="P5" s="16"/>
+      <c r="P5" s="16">
+        <v>0</v>
+      </c>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
@@ -1543,7 +1558,9 @@
       <c r="O6" s="16">
         <v>43</v>
       </c>
-      <c r="P6" s="16"/>
+      <c r="P6" s="16">
+        <v>44</v>
+      </c>
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
       <c r="S6" s="16"/>
@@ -1679,7 +1696,9 @@
       <c r="O7" s="16">
         <v>66</v>
       </c>
-      <c r="P7" s="16"/>
+      <c r="P7" s="16">
+        <v>65</v>
+      </c>
       <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
@@ -1815,7 +1834,9 @@
       <c r="O8" s="16">
         <v>54</v>
       </c>
-      <c r="P8" s="16"/>
+      <c r="P8" s="16">
+        <v>55</v>
+      </c>
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
@@ -1951,7 +1972,9 @@
       <c r="O9" s="16">
         <v>0</v>
       </c>
-      <c r="P9" s="16"/>
+      <c r="P9" s="16">
+        <v>0</v>
+      </c>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
@@ -2087,7 +2110,9 @@
       <c r="O10" s="16">
         <v>24</v>
       </c>
-      <c r="P10" s="16"/>
+      <c r="P10" s="16">
+        <v>23</v>
+      </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
       <c r="S10" s="16"/>
@@ -2223,7 +2248,9 @@
       <c r="O11" s="16">
         <v>0</v>
       </c>
-      <c r="P11" s="16"/>
+      <c r="P11" s="16">
+        <v>0</v>
+      </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16"/>
       <c r="S11" s="16"/>
@@ -2359,7 +2386,9 @@
       <c r="O12" s="16">
         <v>356</v>
       </c>
-      <c r="P12" s="16"/>
+      <c r="P12" s="16">
+        <v>354</v>
+      </c>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
@@ -2495,7 +2524,9 @@
       <c r="O13" s="16">
         <v>986</v>
       </c>
-      <c r="P13" s="16"/>
+      <c r="P13" s="16">
+        <v>985</v>
+      </c>
       <c r="Q13" s="16"/>
       <c r="R13" s="16"/>
       <c r="S13" s="16"/>
@@ -2631,7 +2662,9 @@
       <c r="O14" s="16">
         <v>474</v>
       </c>
-      <c r="P14" s="16"/>
+      <c r="P14" s="16">
+        <v>473</v>
+      </c>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
@@ -2767,7 +2800,9 @@
       <c r="O15" s="16">
         <v>562</v>
       </c>
-      <c r="P15" s="16"/>
+      <c r="P15" s="16">
+        <v>564</v>
+      </c>
       <c r="Q15" s="16"/>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
@@ -2903,7 +2938,9 @@
       <c r="O16" s="16">
         <v>757</v>
       </c>
-      <c r="P16" s="16"/>
+      <c r="P16" s="16">
+        <v>761</v>
+      </c>
       <c r="Q16" s="16"/>
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
@@ -3039,7 +3076,9 @@
       <c r="O17" s="16">
         <v>915</v>
       </c>
-      <c r="P17" s="16"/>
+      <c r="P17" s="16">
+        <v>901</v>
+      </c>
       <c r="Q17" s="16"/>
       <c r="R17" s="16"/>
       <c r="S17" s="16"/>
@@ -3175,7 +3214,9 @@
       <c r="O18" s="17">
         <v>4050</v>
       </c>
-      <c r="P18" s="17"/>
+      <c r="P18" s="17">
+        <v>4038</v>
+      </c>
       <c r="Q18" s="17"/>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
@@ -3416,7 +3457,9 @@
       <c r="O20" s="16">
         <v>4473</v>
       </c>
-      <c r="P20" s="16"/>
+      <c r="P20" s="16">
+        <v>5176</v>
+      </c>
       <c r="Q20" s="16"/>
       <c r="R20" s="16"/>
       <c r="S20" s="16"/>
@@ -3550,7 +3593,9 @@
       <c r="O21" s="16">
         <v>16557</v>
       </c>
-      <c r="P21" s="16"/>
+      <c r="P21" s="16">
+        <v>18975</v>
+      </c>
       <c r="Q21" s="16"/>
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
@@ -3684,7 +3729,9 @@
       <c r="O22" s="16">
         <v>4419</v>
       </c>
-      <c r="P22" s="16"/>
+      <c r="P22" s="16">
+        <v>4989</v>
+      </c>
       <c r="Q22" s="16"/>
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
@@ -3818,7 +3865,9 @@
       <c r="O23" s="16">
         <v>6837</v>
       </c>
-      <c r="P23" s="16"/>
+      <c r="P23" s="16">
+        <v>7484</v>
+      </c>
       <c r="Q23" s="16"/>
       <c r="R23" s="16"/>
       <c r="S23" s="16"/>
@@ -3952,7 +4001,9 @@
       <c r="O24" s="16">
         <v>11172</v>
       </c>
-      <c r="P24" s="16"/>
+      <c r="P24" s="16">
+        <v>11530</v>
+      </c>
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
@@ -4086,7 +4137,9 @@
       <c r="O25" s="16">
         <v>6149</v>
       </c>
-      <c r="P25" s="16"/>
+      <c r="P25" s="16">
+        <v>6674</v>
+      </c>
       <c r="Q25" s="16"/>
       <c r="R25" s="16"/>
       <c r="S25" s="16"/>
@@ -4220,7 +4273,9 @@
       <c r="O26" s="17">
         <v>49607</v>
       </c>
-      <c r="P26" s="17"/>
+      <c r="P26" s="17">
+        <v>54828</v>
+      </c>
       <c r="Q26" s="17"/>
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
@@ -4358,7 +4413,9 @@
       <c r="O27" s="16">
         <v>24469</v>
       </c>
-      <c r="P27" s="16"/>
+      <c r="P27" s="16">
+        <v>23783</v>
+      </c>
       <c r="Q27" s="16"/>
       <c r="R27" s="16"/>
       <c r="S27" s="16"/>
@@ -4476,7 +4533,7 @@
         <v>27655</v>
       </c>
       <c r="H28" s="16">
-        <f t="shared" ref="H28:O28" si="4">H26-H27</f>
+        <f t="shared" ref="H28:P28" si="4">H26-H27</f>
         <v>33569</v>
       </c>
       <c r="I28" s="16">
@@ -4507,7 +4564,10 @@
         <f t="shared" si="4"/>
         <v>25138</v>
       </c>
-      <c r="P28" s="16"/>
+      <c r="P28" s="16">
+        <f t="shared" si="4"/>
+        <v>31045</v>
+      </c>
       <c r="Q28" s="16"/>
       <c r="R28" s="16"/>
       <c r="S28" s="16"/>
@@ -4650,7 +4710,9 @@
       <c r="O29" s="16">
         <v>20830</v>
       </c>
-      <c r="P29" s="16"/>
+      <c r="P29" s="16">
+        <v>22333</v>
+      </c>
       <c r="Q29" s="16"/>
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
@@ -4788,7 +4850,9 @@
       <c r="O30" s="16">
         <v>2795</v>
       </c>
-      <c r="P30" s="16"/>
+      <c r="P30" s="16">
+        <v>2800</v>
+      </c>
       <c r="Q30" s="16"/>
       <c r="R30" s="16"/>
       <c r="S30" s="16"/>
@@ -4926,7 +4990,9 @@
       <c r="O31" s="23">
         <v>-1</v>
       </c>
-      <c r="P31" s="16"/>
+      <c r="P31" s="16">
+        <v>1</v>
+      </c>
       <c r="Q31" s="16"/>
       <c r="R31" s="16"/>
       <c r="S31" s="16"/>
@@ -5044,7 +5110,7 @@
         <v>2077</v>
       </c>
       <c r="H32" s="16">
-        <f t="shared" ref="H32:O32" si="7">H28-SUM(H29:H30)+H31</f>
+        <f t="shared" ref="H32:P32" si="7">H28-SUM(H29:H30)+H31</f>
         <v>7098</v>
       </c>
       <c r="I32" s="16">
@@ -5075,7 +5141,10 @@
         <f t="shared" si="7"/>
         <v>1512</v>
       </c>
-      <c r="P32" s="16"/>
+      <c r="P32" s="16">
+        <f t="shared" si="7"/>
+        <v>5913</v>
+      </c>
       <c r="Q32" s="16"/>
       <c r="R32" s="16"/>
       <c r="S32" s="16"/>
@@ -5219,7 +5288,9 @@
       <c r="O33" s="16">
         <v>-573</v>
       </c>
-      <c r="P33" s="16"/>
+      <c r="P33" s="16">
+        <v>-629</v>
+      </c>
       <c r="Q33" s="16"/>
       <c r="R33" s="16"/>
       <c r="S33" s="16"/>
@@ -5342,7 +5413,7 @@
         <v>1606</v>
       </c>
       <c r="H34" s="16">
-        <f t="shared" ref="H34:O34" si="10">H32+H33</f>
+        <f t="shared" ref="H34:P34" si="10">H32+H33</f>
         <v>6668</v>
       </c>
       <c r="I34" s="16">
@@ -5373,7 +5444,10 @@
         <f t="shared" si="10"/>
         <v>939</v>
       </c>
-      <c r="P34" s="16"/>
+      <c r="P34" s="16">
+        <f t="shared" si="10"/>
+        <v>5284</v>
+      </c>
       <c r="Q34" s="16"/>
       <c r="R34" s="16"/>
       <c r="S34" s="16"/>
@@ -5516,7 +5590,9 @@
       <c r="O35" s="16">
         <v>235</v>
       </c>
-      <c r="P35" s="16"/>
+      <c r="P35" s="16">
+        <v>1321</v>
+      </c>
       <c r="Q35" s="16"/>
       <c r="R35" s="16"/>
       <c r="S35" s="16"/>
@@ -5634,7 +5710,7 @@
         <v>1201</v>
       </c>
       <c r="H36" s="16">
-        <f t="shared" ref="H36:O36" si="14">H34-H35</f>
+        <f t="shared" ref="H36:P36" si="14">H34-H35</f>
         <v>4995</v>
       </c>
       <c r="I36" s="16">
@@ -5665,7 +5741,10 @@
         <f t="shared" si="14"/>
         <v>704</v>
       </c>
-      <c r="P36" s="16"/>
+      <c r="P36" s="16">
+        <f t="shared" si="14"/>
+        <v>3963</v>
+      </c>
       <c r="Q36" s="16"/>
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
@@ -5808,7 +5887,9 @@
       <c r="O37" s="23">
         <v>20</v>
       </c>
-      <c r="P37" s="16"/>
+      <c r="P37" s="16">
+        <v>23</v>
+      </c>
       <c r="Q37" s="16"/>
       <c r="R37" s="16"/>
       <c r="S37" s="16"/>
@@ -5926,7 +6007,7 @@
         <v>1209</v>
       </c>
       <c r="H38" s="16">
-        <f t="shared" ref="H38:O38" si="16">H36+H37</f>
+        <f t="shared" ref="H38:P38" si="16">H36+H37</f>
         <v>5008</v>
       </c>
       <c r="I38" s="16">
@@ -5957,7 +6038,10 @@
         <f t="shared" si="16"/>
         <v>724</v>
       </c>
-      <c r="P38" s="16"/>
+      <c r="P38" s="16">
+        <f t="shared" si="16"/>
+        <v>3986</v>
+      </c>
       <c r="Q38" s="16"/>
       <c r="R38" s="16"/>
       <c r="S38" s="16"/>
@@ -6177,7 +6261,7 @@
         <v>0.74745207867721386</v>
       </c>
       <c r="H40" s="18">
-        <f t="shared" ref="H40:O40" si="18">H38/H41</f>
+        <f t="shared" ref="H40:P40" si="18">H38/H41</f>
         <v>3.1095122014824823</v>
       </c>
       <c r="I40" s="18">
@@ -6208,7 +6292,10 @@
         <f t="shared" si="18"/>
         <v>0.45273881972740621</v>
       </c>
-      <c r="P40" s="18"/>
+      <c r="P40" s="18">
+        <f t="shared" si="18"/>
+        <v>2.4949909270212021</v>
+      </c>
       <c r="Q40" s="18"/>
       <c r="R40" s="18"/>
       <c r="S40" s="18"/>
@@ -6351,7 +6438,9 @@
       <c r="O41" s="3">
         <v>1599.1559999999999</v>
       </c>
-      <c r="P41" s="3"/>
+      <c r="P41" s="3">
+        <v>1597.6010000000001</v>
+      </c>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
@@ -6585,7 +6674,10 @@
         <f>+O26/K26-1</f>
         <v>-0.10348255109970539</v>
       </c>
-      <c r="P43" s="19"/>
+      <c r="P43" s="19">
+        <f>+P26/L26-1</f>
+        <v>-3.3254575589801494E-2</v>
+      </c>
       <c r="Q43" s="19"/>
       <c r="R43" s="19"/>
       <c r="S43" s="20"/>
@@ -6736,16 +6828,19 @@
         <f t="shared" si="25"/>
         <v>0.50674299997984151</v>
       </c>
-      <c r="P44" s="21"/>
+      <c r="P44" s="21">
+        <f t="shared" ref="P44" si="26">P28/P26</f>
+        <v>0.5662252863500401</v>
+      </c>
       <c r="Q44" s="21"/>
       <c r="R44" s="21"/>
       <c r="S44" s="3"/>
       <c r="T44" s="21">
-        <f t="shared" ref="T44:U44" si="26">T28/T26</f>
+        <f t="shared" ref="T44:U44" si="27">T28/T26</f>
         <v>0.52775585901179589</v>
       </c>
       <c r="U44" s="21">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.50712806359118423</v>
       </c>
       <c r="V44" s="21">
@@ -6839,19 +6934,19 @@
         <v>30</v>
       </c>
       <c r="C45" s="21">
-        <f t="shared" ref="C45:F45" si="27">C32/C26</f>
+        <f t="shared" ref="C45:F45" si="28">C32/C26</f>
         <v>1.3212567429654468E-2</v>
       </c>
       <c r="D45" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8.2286170508192175E-2</v>
       </c>
       <c r="E45" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7.781992544788742E-2</v>
       </c>
       <c r="F45" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6.9146049481245017E-2</v>
       </c>
       <c r="G45" s="21">
@@ -6859,47 +6954,50 @@
         <v>3.8700180737483464E-2</v>
       </c>
       <c r="H45" s="21">
-        <f t="shared" ref="H45:K45" si="28">H32/H26</f>
+        <f t="shared" ref="H45:K45" si="29">H32/H26</f>
         <v>0.11908396946564885</v>
       </c>
       <c r="I45" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>5.9429597871583265E-2</v>
       </c>
       <c r="J45" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.43492032865435E-2</v>
       </c>
       <c r="K45" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2.1741094825872446E-2</v>
       </c>
       <c r="L45" s="21">
-        <f t="shared" ref="L45:M45" si="29">L32/L26</f>
+        <f t="shared" ref="L45:M45" si="30">L32/L26</f>
         <v>0.10427760341361922</v>
       </c>
       <c r="M45" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8.6184822070610526E-2</v>
       </c>
       <c r="N45" s="21">
-        <f t="shared" ref="N45:O45" si="30">N32/N26</f>
+        <f t="shared" ref="N45:O45" si="31">N32/N26</f>
         <v>0.10746188007632428</v>
       </c>
       <c r="O45" s="21">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3.0479569415606669E-2</v>
       </c>
-      <c r="P45" s="21"/>
+      <c r="P45" s="21">
+        <f t="shared" ref="P45" si="32">P32/P26</f>
+        <v>0.10784635587655943</v>
+      </c>
       <c r="Q45" s="21"/>
       <c r="R45" s="21"/>
       <c r="S45" s="3"/>
       <c r="T45" s="21">
-        <f t="shared" ref="T45:U45" si="31">T32/T26</f>
+        <f t="shared" ref="T45:U45" si="33">T32/T26</f>
         <v>7.6671005744671228E-2</v>
       </c>
       <c r="U45" s="21">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3.206845803903325E-2</v>
       </c>
       <c r="V45" s="21">
@@ -6993,19 +7091,19 @@
         <v>31</v>
       </c>
       <c r="C46" s="21">
-        <f t="shared" ref="C46:F46" si="32">C38/C26</f>
+        <f t="shared" ref="C46:F46" si="34">C38/C26</f>
         <v>9.8593089371628514E-3</v>
       </c>
       <c r="D46" s="21">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>5.7206331574562619E-2</v>
       </c>
       <c r="E46" s="21">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>5.4649654334367866E-2</v>
       </c>
       <c r="F46" s="21">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>2.5331205107741419E-2</v>
       </c>
       <c r="G46" s="21">
@@ -7013,47 +7111,50 @@
         <v>2.2526970877042612E-2</v>
       </c>
       <c r="H46" s="21">
-        <f t="shared" ref="H46:K46" si="33">H38/H26</f>
+        <f t="shared" ref="H46:K46" si="35">H38/H26</f>
         <v>8.401979699689624E-2</v>
       </c>
       <c r="I46" s="21">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3.9297758045110237E-2</v>
       </c>
       <c r="J46" s="21">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>4.9603653144244531E-2</v>
       </c>
       <c r="K46" s="21">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1.066271483563154E-2</v>
       </c>
       <c r="L46" s="21">
-        <f t="shared" ref="L46:M46" si="34">L38/L26</f>
+        <f t="shared" ref="L46:M46" si="36">L38/L26</f>
         <v>7.0123778961103084E-2</v>
       </c>
       <c r="M46" s="21">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>5.6632232492063769E-2</v>
       </c>
       <c r="N46" s="21">
-        <f t="shared" ref="N46:O46" si="35">N38/N26</f>
+        <f t="shared" ref="N46:O46" si="37">N38/N26</f>
         <v>7.3656304351496935E-2</v>
       </c>
       <c r="O46" s="21">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>1.4594714455621183E-2</v>
       </c>
-      <c r="P46" s="21"/>
+      <c r="P46" s="21">
+        <f t="shared" ref="P46" si="38">P38/P26</f>
+        <v>7.2700080250966664E-2</v>
+      </c>
       <c r="Q46" s="21"/>
       <c r="R46" s="21"/>
       <c r="S46" s="3"/>
       <c r="T46" s="21">
-        <f t="shared" ref="T46:U46" si="36">T38/T26</f>
+        <f t="shared" ref="T46:U46" si="39">T38/T26</f>
         <v>5.5335809455839408E-2</v>
       </c>
       <c r="U46" s="21">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>1.5951474594391488E-2</v>
       </c>
       <c r="V46" s="21">
@@ -7147,19 +7248,19 @@
         <v>32</v>
       </c>
       <c r="C47" s="21">
-        <f t="shared" ref="C47:F47" si="37">C35/C34</f>
+        <f t="shared" ref="C47:F47" si="40">C35/C34</f>
         <v>-0.36363636363636365</v>
       </c>
       <c r="D47" s="21">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.23976878612716762</v>
       </c>
       <c r="E47" s="21">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.24102446832837868</v>
       </c>
       <c r="F47" s="21">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.59754851889683347</v>
       </c>
       <c r="G47" s="21">
@@ -7167,47 +7268,50 @@
         <v>0.25217932752179328</v>
       </c>
       <c r="H47" s="21">
-        <f t="shared" ref="H47:K47" si="38">H35/H34</f>
+        <f t="shared" ref="H47:K47" si="41">H35/H34</f>
         <v>0.25089982003599282</v>
       </c>
       <c r="I47" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.25218800648298217</v>
       </c>
       <c r="J47" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.24559255631733595</v>
       </c>
       <c r="K47" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.24015748031496062</v>
       </c>
       <c r="L47" s="21">
-        <f t="shared" ref="L47:M47" si="39">L35/L34</f>
+        <f t="shared" ref="L47:M47" si="42">L35/L34</f>
         <v>0.25118125118125118</v>
       </c>
       <c r="M47" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.25682554372975475</v>
       </c>
       <c r="N47" s="21">
-        <f t="shared" ref="N47:O47" si="40">N35/N34</f>
+        <f t="shared" ref="N47:O47" si="43">N35/N34</f>
         <v>0.25656426977861679</v>
       </c>
       <c r="O47" s="21">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.25026624068157616</v>
       </c>
-      <c r="P47" s="21"/>
+      <c r="P47" s="21">
+        <f t="shared" ref="P47" si="44">P35/P34</f>
+        <v>0.25</v>
+      </c>
       <c r="Q47" s="21"/>
       <c r="R47" s="21"/>
       <c r="S47" s="3"/>
       <c r="T47" s="21">
-        <f t="shared" ref="T47:U47" si="41">T35/T34</f>
+        <f t="shared" ref="T47:U47" si="45">T35/T34</f>
         <v>0.23006993006993007</v>
       </c>
       <c r="U47" s="21">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.42631917631917632</v>
       </c>
       <c r="V47" s="21">
